--- a/mistral_translate_work/split_by_prompt/excel/name_title/lang_multi_text/lang_multi_text__name_title__part_0061.xlsx
+++ b/mistral_translate_work/split_by_prompt/excel/name_title/lang_multi_text/lang_multi_text__name_title__part_0061.xlsx
@@ -714,7 +714,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>Special Dodge</t>
+          <t>Né Tránh Đặc Biệt</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -994,7 +994,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>Plunging Attack</t>
+          <t>Tấn Công Đâm Xuống</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -1134,7 +1134,7 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>Sonance Casket</t>
+          <t>Hòm Thanh Âm</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -1204,7 +1204,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>Synthesizer</t>
+          <t>Bộ tổng hợp</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -1274,7 +1274,7 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>Immobilize</t>
+          <t>Hóa Bất Động</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
@@ -1344,7 +1344,7 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>Counterattack</t>
+          <t>Phản công</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
@@ -1414,7 +1414,7 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>Dodge</t>
+          <t>Né tránh</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
@@ -1484,7 +1484,7 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>Immobilize</t>
+          <t>Hóa Bất Động</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
@@ -1624,7 +1624,7 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>Bom Nổ &amp; Bộ Phận Bay</t>
+          <t>Bom nổ &amp; Bộ nâng</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
@@ -1694,7 +1694,7 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>Sensor</t>
+          <t>Cảm Biến</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
@@ -1764,7 +1764,7 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>Điểm Kinh Nghiệm Liên Minh &amp; Cấp Độ Liên Minh</t>
+          <t>Kinh nghiệm &amp; Cấp Liên Minh</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
@@ -1834,7 +1834,7 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>Công cụ</t>
+          <t>Tiện ích</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
@@ -1904,7 +1904,7 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>Di chuyển nhanh</t>
+          <t>Dịch chuyển nhanh</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
@@ -1974,7 +1974,7 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>Rally</t>
+          <t>Tập Hợp</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
@@ -2044,7 +2044,7 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>Attack Weak Point</t>
+          <t>Tấn Công Điểm Yếu</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
@@ -2114,7 +2114,7 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>SOL3 Thăng Tiến Pha: I</t>
+          <t>Thăng Tiến Pha SOL3: I</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
@@ -2184,7 +2184,7 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>Tacet Field: Phần thưởng</t>
+          <t>Tổ Tacet: Phần Thưởng</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
@@ -2254,7 +2254,7 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>Sonance Casket Delivery</t>
+          <t>Giao Hòm Thanh Âm</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
@@ -2324,7 +2324,7 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>Simulation Training Ground</t>
+          <t>Khu Huấn Luyện Mô Phỏng</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
@@ -2394,7 +2394,7 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>Sonance Casket</t>
+          <t>Hòm Thanh Âm</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
@@ -2534,7 +2534,7 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>Training Dummy</t>
+          <t>Bù Nhìn Huấn Luyện</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
@@ -2604,7 +2604,7 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>Propulsion Flux</t>
+          <t>Dòng Đẩy Xung Lực</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
@@ -2674,7 +2674,7 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>Cấp Độ Liên Minh &amp; Kinh Nghiệm Liên Minh</t>
+          <t>Cấp Liên Minh &amp; Kinh nghiệm</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
@@ -2744,7 +2744,7 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>Cấp Độ Kho Dữ Liệu</t>
+          <t>Cấp Độ Ngân Hàng Dữ Liệu</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
@@ -2814,7 +2814,7 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>Echo Challenge: Gulpuff</t>
+          <t>Thử Thách Tiếng Vọng: Gulpuff</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
@@ -2884,7 +2884,7 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>Capture Frequency Signal</t>
+          <t>Thu Tần Số</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
@@ -2954,7 +2954,7 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>Track Acoustic Print</t>
+          <t>Bản nhạc Acoustic Print</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
@@ -3024,7 +3024,7 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>Zoom Camera</t>
+          <t>Thu nhỏ/Góc rộng</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
@@ -3094,7 +3094,7 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>Tacetite Fulminate &amp; Fissured Ledge</t>
+          <t>Sấm Sét Tacetite &amp; Vách Đá Nứt</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
@@ -4144,7 +4144,7 @@
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>Autopuppet Scout</t>
+          <t>Trinh Sát Tự Động</t>
         </is>
       </c>
       <c r="N53" t="inlineStr">
@@ -4634,7 +4634,7 @@
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t>Lioness of Glory</t>
+          <t>Sư Tử Vinh Quang - Giai Đoạn Truy Cập Sớm</t>
         </is>
       </c>
       <c r="N60" t="inlineStr">
@@ -4774,7 +4774,7 @@
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t>Pilgrim's Shell</t>
+          <t>Vỏ Sò Hành Hương</t>
         </is>
       </c>
       <c r="N62" t="inlineStr">
@@ -4844,7 +4844,7 @@
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t>Gladiator</t>
+          <t>Đấu sĩ</t>
         </is>
       </c>
       <c r="N63" t="inlineStr">
@@ -4984,7 +4984,7 @@
       </c>
       <c r="M65" t="inlineStr">
         <is>
-          <t>SOL3 Thăng Tiến Pha: II</t>
+          <t>Thăng Tiến Pha SOL3: II</t>
         </is>
       </c>
       <c r="N65" t="inlineStr">
@@ -5054,7 +5054,7 @@
       </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t>Prestige Points</t>
+          <t>Điểm Uy Tín</t>
         </is>
       </c>
       <c r="N66" t="inlineStr">
@@ -5194,7 +5194,7 @@
       </c>
       <c r="M68" t="inlineStr">
         <is>
-          <t>Spikes &amp; Corroders</t>
+          <t>Gai Nhọn &amp; Kẻ Ăn Mòn</t>
         </is>
       </c>
       <c r="N68" t="inlineStr">
@@ -5264,7 +5264,7 @@
       </c>
       <c r="M69" t="inlineStr">
         <is>
-          <t>Induction Cell &amp; Induction Cell Socket</t>
+          <t>Ô Nhiễm Điện &amp; Khe Ô Nhiễm Điện</t>
         </is>
       </c>
       <c r="N69" t="inlineStr">
@@ -5334,7 +5334,7 @@
       </c>
       <c r="M70" t="inlineStr">
         <is>
-          <t>Transducer</t>
+          <t>Bộ chuyển đổi</t>
         </is>
       </c>
       <c r="N70" t="inlineStr">
@@ -5404,7 +5404,7 @@
       </c>
       <c r="M71" t="inlineStr">
         <is>
-          <t>Fragile Rock</t>
+          <t>Đá Mỏng Manh</t>
         </is>
       </c>
       <c r="N71" t="inlineStr">
@@ -5474,7 +5474,7 @@
       </c>
       <c r="M72" t="inlineStr">
         <is>
-          <t>Road Sign</t>
+          <t>Biển Chỉ Đường</t>
         </is>
       </c>
       <c r="N72" t="inlineStr">
@@ -5544,7 +5544,7 @@
       </c>
       <c r="M73" t="inlineStr">
         <is>
-          <t>Tactical Hologram: Thử Thách</t>
+          <t>Bản Hologram Chiến Thuật: Thử Thách</t>
         </is>
       </c>
       <c r="N73" t="inlineStr">
@@ -5614,7 +5614,7 @@
       </c>
       <c r="M74" t="inlineStr">
         <is>
-          <t>Sound Emulator</t>
+          <t>Bộ Mô Phỏng Âm Thanh</t>
         </is>
       </c>
       <c r="N74" t="inlineStr">
@@ -5684,7 +5684,7 @@
       </c>
       <c r="M75" t="inlineStr">
         <is>
-          <t>Tactical Hologram: Overdash</t>
+          <t>Hologram Chiến Thuật: Overdash</t>
         </is>
       </c>
       <c r="N75" t="inlineStr">
@@ -5754,7 +5754,7 @@
       </c>
       <c r="M76" t="inlineStr">
         <is>
-          <t>Overdashing Mô-đun</t>
+          <t>Mô-đun Bay vượt tốc</t>
         </is>
       </c>
       <c r="N76" t="inlineStr">
@@ -5824,7 +5824,7 @@
       </c>
       <c r="M77" t="inlineStr">
         <is>
-          <t>Signals Hub &amp; Signals Console</t>
+          <t>Trung tâm &amp; Bảng điều khiển Tín hiệu</t>
         </is>
       </c>
       <c r="N77" t="inlineStr">
@@ -5894,7 +5894,7 @@
       </c>
       <c r="M78" t="inlineStr">
         <is>
-          <t>Pressure Platform &amp; Weight Block</t>
+          <t>Nền Đỡ Áp Lực &amp; Khối Tạ</t>
         </is>
       </c>
       <c r="N78" t="inlineStr">
@@ -5964,7 +5964,7 @@
       </c>
       <c r="M79" t="inlineStr">
         <is>
-          <t>Energy Matrix</t>
+          <t>Ma Trận Năng Lượng</t>
         </is>
       </c>
       <c r="N79" t="inlineStr">
@@ -6034,7 +6034,7 @@
       </c>
       <c r="M80" t="inlineStr">
         <is>
-          <t>Encryption Block</t>
+          <t>Khối Mã Hóa</t>
         </is>
       </c>
       <c r="N80" t="inlineStr">
@@ -6104,7 +6104,7 @@
       </c>
       <c r="M81" t="inlineStr">
         <is>
-          <t>Grapple</t>
+          <t>Móc Câu</t>
         </is>
       </c>
       <c r="N81" t="inlineStr">
@@ -6174,7 +6174,7 @@
       </c>
       <c r="M82" t="inlineStr">
         <is>
-          <t>Grapple Shooter</t>
+          <t>Súng Móc</t>
         </is>
       </c>
       <c r="N82" t="inlineStr">
@@ -6314,7 +6314,7 @@
       </c>
       <c r="M84" t="inlineStr">
         <is>
-          <t>Vine Trap &amp; Explosive Charge</t>
+          <t>Bẫy Dây Leo &amp; Đầu Đạn Nổ</t>
         </is>
       </c>
       <c r="N84" t="inlineStr">
@@ -6384,7 +6384,7 @@
       </c>
       <c r="M85" t="inlineStr">
         <is>
-          <t>Vine Trap</t>
+          <t>Bẫy Dây Leo</t>
         </is>
       </c>
       <c r="N85" t="inlineStr">
@@ -6454,7 +6454,7 @@
       </c>
       <c r="M86" t="inlineStr">
         <is>
-          <t>Magnetic Cube</t>
+          <t>Khối Từ Tính</t>
         </is>
       </c>
       <c r="N86" t="inlineStr">
@@ -6524,7 +6524,7 @@
       </c>
       <c r="M87" t="inlineStr">
         <is>
-          <t>Echo Challenge: Cruisewing</t>
+          <t>Thử Thách Tiếng Vọng: Cruisewing</t>
         </is>
       </c>
       <c r="N87" t="inlineStr">
@@ -6594,7 +6594,7 @@
       </c>
       <c r="M88" t="inlineStr">
         <is>
-          <t>Blobfly</t>
+          <t>Ruồi Bóng</t>
         </is>
       </c>
       <c r="N88" t="inlineStr">
@@ -6664,7 +6664,7 @@
       </c>
       <c r="M89" t="inlineStr">
         <is>
-          <t>Gravitation Vortex</t>
+          <t>Xoáy Hấp Dẫn</t>
         </is>
       </c>
       <c r="N89" t="inlineStr">
@@ -6734,7 +6734,7 @@
       </c>
       <c r="M90" t="inlineStr">
         <is>
-          <t>Backflip</t>
+          <t>Lộn người về sau</t>
         </is>
       </c>
       <c r="N90" t="inlineStr">
@@ -6804,7 +6804,7 @@
       </c>
       <c r="M91" t="inlineStr">
         <is>
-          <t>Transmit Frequency Signal</t>
+          <t>Truyền Tín Hiệu Tần Số</t>
         </is>
       </c>
       <c r="N91" t="inlineStr">
@@ -6874,7 +6874,7 @@
       </c>
       <c r="M92" t="inlineStr">
         <is>
-          <t>Fragile Surface Rock</t>
+          <t>Đá Bề Mặt Mỏng Manh</t>
         </is>
       </c>
       <c r="N92" t="inlineStr">
@@ -6944,7 +6944,7 @@
       </c>
       <c r="M93" t="inlineStr">
         <is>
-          <t>Control Puppet</t>
+          <t>Điều khiển Bù nhìn</t>
         </is>
       </c>
       <c r="N93" t="inlineStr">
@@ -7014,7 +7014,7 @@
       </c>
       <c r="M94" t="inlineStr">
         <is>
-          <t>Rotate Space</t>
+          <t>Xoay Không Gian</t>
         </is>
       </c>
       <c r="N94" t="inlineStr">
@@ -7084,7 +7084,7 @@
       </c>
       <c r="M95" t="inlineStr">
         <is>
-          <t>Hit Ground Mechanism</t>
+          <t>Cơ chế Đòn Đánh Mặt Đất</t>
         </is>
       </c>
       <c r="N95" t="inlineStr">
@@ -7154,7 +7154,7 @@
       </c>
       <c r="M96" t="inlineStr">
         <is>
-          <t>Spinning Mechanism</t>
+          <t>Cơ Chế Xoay</t>
         </is>
       </c>
       <c r="N96" t="inlineStr">
@@ -7224,7 +7224,7 @@
       </c>
       <c r="M97" t="inlineStr">
         <is>
-          <t>Toxic Fog Concentration</t>
+          <t>Nồng Độ Sương Mù Độc Hại</t>
         </is>
       </c>
       <c r="N97" t="inlineStr">
@@ -7294,7 +7294,7 @@
       </c>
       <c r="M98" t="inlineStr">
         <is>
-          <t>Tactical Hologram: Detonate</t>
+          <t>Bản Hologram Chiến Thuật: Kích Nổ</t>
         </is>
       </c>
       <c r="N98" t="inlineStr">
@@ -7364,7 +7364,7 @@
       </c>
       <c r="M99" t="inlineStr">
         <is>
-          <t>Overdash Club</t>
+          <t>Câu lạc bộ Bay vượt tốc</t>
         </is>
       </c>
       <c r="N99" t="inlineStr">
@@ -7434,7 +7434,7 @@
       </c>
       <c r="M100" t="inlineStr">
         <is>
-          <t>Signal Decoder</t>
+          <t>Bộ giải mã tín hiệu</t>
         </is>
       </c>
       <c r="N100" t="inlineStr">
@@ -7504,7 +7504,7 @@
       </c>
       <c r="M101" t="inlineStr">
         <is>
-          <t>Banner of Victory</t>
+          <t>Ngọn Cờ Chiến Thắng</t>
         </is>
       </c>
       <c r="N101" t="inlineStr">
@@ -7574,7 +7574,7 @@
       </c>
       <c r="M102" t="inlineStr">
         <is>
-          <t>Occupying Banners</t>
+          <t>Chiếm giữ Cờ hiệu</t>
         </is>
       </c>
       <c r="N102" t="inlineStr">
@@ -7644,7 +7644,7 @@
       </c>
       <c r="M103" t="inlineStr">
         <is>
-          <t>Special Banners</t>
+          <t>Các Banner Đặc Biệt</t>
         </is>
       </c>
       <c r="N103" t="inlineStr">
@@ -7714,7 +7714,7 @@
       </c>
       <c r="M104" t="inlineStr">
         <is>
-          <t>Battle Engagement Points</t>
+          <t>Điểm Tham Chiến</t>
         </is>
       </c>
       <c r="N104" t="inlineStr">
@@ -7784,7 +7784,7 @@
       </c>
       <c r="M105" t="inlineStr">
         <is>
-          <t>Dream Contagion</t>
+          <t>Lây Nhiễm Mộng</t>
         </is>
       </c>
       <c r="N105" t="inlineStr">
@@ -7854,7 +7854,7 @@
       </c>
       <c r="M106" t="inlineStr">
         <is>
-          <t>Dream Contagion: Kerasaur</t>
+          <t>Ác Mộng Truyền Nhiễm: Kerasaur</t>
         </is>
       </c>
       <c r="N106" t="inlineStr">
@@ -7924,7 +7924,7 @@
       </c>
       <c r="M107" t="inlineStr">
         <is>
-          <t>Dream Contagion: Drakes</t>
+          <t>Ác Mộng Truyền Nhiễm: Drakes</t>
         </is>
       </c>
       <c r="N107" t="inlineStr">
@@ -7994,7 +7994,7 @@
       </c>
       <c r="M108" t="inlineStr">
         <is>
-          <t>Dream Contagion: Gladiators</t>
+          <t>Ác Mộng Truyền Nhiễm: Gladiators</t>
         </is>
       </c>
       <c r="N108" t="inlineStr">
@@ -8064,7 +8064,7 @@
       </c>
       <c r="M109" t="inlineStr">
         <is>
-          <t>Dream Contagion: Pilgrim's Shell</t>
+          <t>Ác Mộng Truyền Nhiễm: Vỏ Hành Hương</t>
         </is>
       </c>
       <c r="N109" t="inlineStr">
@@ -8134,7 +8134,7 @@
       </c>
       <c r="M110" t="inlineStr">
         <is>
-          <t>Septimont Patrol Unit</t>
+          <t>Đơn Vị Tuần Tra Septimont</t>
         </is>
       </c>
       <c r="N110" t="inlineStr">
@@ -8204,7 +8204,7 @@
       </c>
       <c r="M111" t="inlineStr">
         <is>
-          <t>Hero's Slash</t>
+          <t>Thái Anh Hùng</t>
         </is>
       </c>
       <c r="N111" t="inlineStr">
@@ -8274,7 +8274,7 @@
       </c>
       <c r="M112" t="inlineStr">
         <is>
-          <t>Hero's Rend</t>
+          <t>Phách Anh Hùng</t>
         </is>
       </c>
       <c r="N112" t="inlineStr">
@@ -8344,7 +8344,7 @@
       </c>
       <c r="M113" t="inlineStr">
         <is>
-          <t>Bitter Resentment</t>
+          <t>Oán Hận Đắng Cay</t>
         </is>
       </c>
       <c r="N113" t="inlineStr">
@@ -8414,7 +8414,7 @@
       </c>
       <c r="M114" t="inlineStr">
         <is>
-          <t>Speedrail</t>
+          <t>Đường Ray Tốc Độ</t>
         </is>
       </c>
       <c r="N114" t="inlineStr">
@@ -8484,7 +8484,7 @@
       </c>
       <c r="M115" t="inlineStr">
         <is>
-          <t>Vitreum Dancer: Slowdown</t>
+          <t>Vũ Công Pha Lê: Slowdown</t>
         </is>
       </c>
       <c r="N115" t="inlineStr">
@@ -8554,7 +8554,7 @@
       </c>
       <c r="M116" t="inlineStr">
         <is>
-          <t>Hero's Impact: Slash</t>
+          <t>Tác Động Anh Hùng: Vết Chém</t>
         </is>
       </c>
       <c r="N116" t="inlineStr">
@@ -8624,7 +8624,7 @@
       </c>
       <c r="M117" t="inlineStr">
         <is>
-          <t>Hero's Impact: Precision Slash</t>
+          <t>Tác Động Anh Hùng: Vết Chém Chính Xác</t>
         </is>
       </c>
       <c r="N117" t="inlineStr">
@@ -8694,7 +8694,7 @@
       </c>
       <c r="M118" t="inlineStr">
         <is>
-          <t>Ta-da's Protection: Speed Hooray</t>
+          <t>Bảo Vệ Của Ta-da: Nhanh Tay Hoan Hô</t>
         </is>
       </c>
       <c r="N118" t="inlineStr">
@@ -8764,7 +8764,7 @@
       </c>
       <c r="M119" t="inlineStr">
         <is>
-          <t>Banner of Victory</t>
+          <t>Ngọn Cờ Chiến Thắng</t>
         </is>
       </c>
       <c r="N119" t="inlineStr">
@@ -8834,7 +8834,7 @@
       </c>
       <c r="M120" t="inlineStr">
         <is>
-          <t>Peaks of Prestige: Xây Dựng Bộ Đệm</t>
+          <t>Peaks of Prestige: Xây dựng Bộ Bài</t>
         </is>
       </c>
       <c r="N120" t="inlineStr">
@@ -8904,7 +8904,7 @@
       </c>
       <c r="M121" t="inlineStr">
         <is>
-          <t>Basic Rules</t>
+          <t>Quy Tắc Cơ Bản</t>
         </is>
       </c>
       <c r="N121" t="inlineStr">
@@ -8974,7 +8974,7 @@
       </c>
       <c r="M122" t="inlineStr">
         <is>
-          <t>Biến Đổi</t>
+          <t>Biến hình</t>
         </is>
       </c>
       <c r="N122" t="inlineStr">
@@ -9114,7 +9114,7 @@
       </c>
       <c r="M124" t="inlineStr">
         <is>
-          <t>Echo Cốt lõi</t>
+          <t>Tiếng Vọng Cốt Lõi</t>
         </is>
       </c>
       <c r="N124" t="inlineStr">
@@ -9184,7 +9184,7 @@
       </c>
       <c r="M125" t="inlineStr">
         <is>
-          <t>Cruisewing Echo Challenge</t>
+          <t>Thử Thách Tiếng Vọng Cruisewing</t>
         </is>
       </c>
       <c r="N125" t="inlineStr">
@@ -9254,7 +9254,7 @@
       </c>
       <c r="M126" t="inlineStr">
         <is>
-          <t>Incinero Petal</t>
+          <t>Cánh Hoa Incinero</t>
         </is>
       </c>
       <c r="N126" t="inlineStr">
@@ -9324,7 +9324,7 @@
       </c>
       <c r="M127" t="inlineStr">
         <is>
-          <t>Spear Tip: Penetration Test</t>
+          <t>Thử Nghiệm Khả Năng Xuyên Thấu Đầu Lao</t>
         </is>
       </c>
       <c r="N127" t="inlineStr">
@@ -9394,7 +9394,7 @@
       </c>
       <c r="M128" t="inlineStr">
         <is>
-          <t>Spear Breech: Propeller Test</t>
+          <t>Thử Nghiệm Cánh Quạt Đuôi Lao</t>
         </is>
       </c>
       <c r="N128" t="inlineStr">
@@ -9464,7 +9464,7 @@
       </c>
       <c r="M129" t="inlineStr">
         <is>
-          <t>Spear Barrel: Durability Test</t>
+          <t>Thử Nghiệm Độ Bền Thân Lao</t>
         </is>
       </c>
       <c r="N129" t="inlineStr">
@@ -9534,7 +9534,7 @@
       </c>
       <c r="M130" t="inlineStr">
         <is>
-          <t>Explosive Spear</t>
+          <t>Thương Nổ</t>
         </is>
       </c>
       <c r="N130" t="inlineStr">
@@ -9604,7 +9604,7 @@
       </c>
       <c r="M131" t="inlineStr">
         <is>
-          <t>Biến Hình thành Inferno Rider</t>
+          <t>Biến hình thành Kỵ Sĩ Hỏa Ngục</t>
         </is>
       </c>
       <c r="N131" t="inlineStr">
@@ -9674,7 +9674,7 @@
       </c>
       <c r="M132" t="inlineStr">
         <is>
-          <t>Ultrasonic Pulse Chip</t>
+          <t>Chip Xung Siêu Âm</t>
         </is>
       </c>
       <c r="N132" t="inlineStr">
@@ -9744,7 +9744,7 @@
       </c>
       <c r="M133" t="inlineStr">
         <is>
-          <t>Swamp Vortex</t>
+          <t>Xoáy Lầy Tử Thần</t>
         </is>
       </c>
       <c r="N133" t="inlineStr">
@@ -9814,7 +9814,7 @@
       </c>
       <c r="M134" t="inlineStr">
         <is>
-          <t>Suppressor</t>
+          <t>Bộ Áp Chế</t>
         </is>
       </c>
       <c r="N134" t="inlineStr">
@@ -9884,7 +9884,7 @@
       </c>
       <c r="M135" t="inlineStr">
         <is>
-          <t>Mud</t>
+          <t>Bùn đất</t>
         </is>
       </c>
       <c r="N135" t="inlineStr">
@@ -9954,7 +9954,7 @@
       </c>
       <c r="M136" t="inlineStr">
         <is>
-          <t>Clear Toxic Spores: Offshoot Core</t>
+          <t>Diệt trừ Bào Tử Độc: Nhân Tâm Nhánh</t>
         </is>
       </c>
       <c r="N136" t="inlineStr">
@@ -10024,7 +10024,7 @@
       </c>
       <c r="M137" t="inlineStr">
         <is>
-          <t>Basic Attack Tutorial: Taoqi</t>
+          <t>Hướng Dẫn Đòn Cơ Bản: Taoqi</t>
         </is>
       </c>
       <c r="N137" t="inlineStr">
@@ -10094,7 +10094,7 @@
       </c>
       <c r="M138" t="inlineStr">
         <is>
-          <t>Dấu Vết Thủy Triều</t>
+          <t>Dấu vết của Thủy Triều</t>
         </is>
       </c>
       <c r="N138" t="inlineStr">
@@ -10164,7 +10164,7 @@
       </c>
       <c r="M139" t="inlineStr">
         <is>
-          <t>Basic Attack Tutorial: Taoqi</t>
+          <t>Hướng Dẫn Đòn Cơ Bản: Taoqi</t>
         </is>
       </c>
       <c r="N139" t="inlineStr">
@@ -10234,7 +10234,7 @@
       </c>
       <c r="M140" t="inlineStr">
         <is>
-          <t>Basic Attack Tutorial: Taoqi</t>
+          <t>Hướng Dẫn Đòn Cơ Bản: Taoqi</t>
         </is>
       </c>
       <c r="N140" t="inlineStr">
@@ -10304,7 +10304,7 @@
       </c>
       <c r="M141" t="inlineStr">
         <is>
-          <t>Skill Tutorial: Taoqi</t>
+          <t>Hướng Dẫn Kỹ Năng: Taoqi</t>
         </is>
       </c>
       <c r="N141" t="inlineStr">
@@ -10374,7 +10374,7 @@
       </c>
       <c r="M142" t="inlineStr">
         <is>
-          <t>Skill Tutorial: Taoqi</t>
+          <t>Hướng Dẫn Kỹ Năng: Taoqi</t>
         </is>
       </c>
       <c r="N142" t="inlineStr">
@@ -10444,7 +10444,7 @@
       </c>
       <c r="M143" t="inlineStr">
         <is>
-          <t>Skill Tutorial: Taoqi</t>
+          <t>Hướng Dẫn Kỹ Năng: Taoqi</t>
         </is>
       </c>
       <c r="N143" t="inlineStr">
@@ -10514,7 +10514,7 @@
       </c>
       <c r="M144" t="inlineStr">
         <is>
-          <t>Đội Comp Tutorial: Taoqi</t>
+          <t>Hướng dẫn Đội Hình: Taoqi</t>
         </is>
       </c>
       <c r="N144" t="inlineStr">
@@ -10584,7 +10584,7 @@
       </c>
       <c r="M145" t="inlineStr">
         <is>
-          <t>Đội Comp Tutorial: Taoqi</t>
+          <t>Hướng dẫn Đội Hình: Taoqi</t>
         </is>
       </c>
       <c r="N145" t="inlineStr">
@@ -10654,7 +10654,7 @@
       </c>
       <c r="M146" t="inlineStr">
         <is>
-          <t>Triệu Tập Details</t>
+          <t>Chi tiết triệu tập</t>
         </is>
       </c>
       <c r="N146" t="inlineStr">
@@ -10724,7 +10724,7 @@
       </c>
       <c r="M147" t="inlineStr">
         <is>
-          <t>Đăng Ký Lunite</t>
+          <t>Lunite Subscription</t>
         </is>
       </c>
       <c r="N147" t="inlineStr">
@@ -10934,7 +10934,7 @@
       </c>
       <c r="M150" t="inlineStr">
         <is>
-          <t>Vượt Sóng</t>
+          <t>Vượt Qua Những Con Sóng</t>
         </is>
       </c>
       <c r="N150" t="inlineStr">
@@ -11004,7 +11004,7 @@
       </c>
       <c r="M151" t="inlineStr">
         <is>
-          <t>Giải Thích Điểm Mở Khóa</t>
+          <t>Mở khóa Giải Thích Điểm.</t>
         </is>
       </c>
       <c r="N151" t="inlineStr">
@@ -11074,7 +11074,7 @@
       </c>
       <c r="M152" t="inlineStr">
         <is>
-          <t>Acropolis Documentarian</t>
+          <t>Nhà Biên Ký Acropolis</t>
         </is>
       </c>
       <c r="N152" t="inlineStr">
@@ -11144,7 +11144,7 @@
       </c>
       <c r="M153" t="inlineStr">
         <is>
-          <t>Resonator Introduction: Verina</t>
+          <t>Giới Thiệu Resonator: Verina</t>
         </is>
       </c>
       <c r="N153" t="inlineStr">
@@ -11214,7 +11214,7 @@
       </c>
       <c r="M154" t="inlineStr">
         <is>
-          <t>Resonator Introduction: Verina</t>
+          <t>Giới Thiệu Resonator: Verina</t>
         </is>
       </c>
       <c r="N154" t="inlineStr">
@@ -11284,7 +11284,7 @@
       </c>
       <c r="M155" t="inlineStr">
         <is>
-          <t>Resonator Introduction: Verina</t>
+          <t>Giới Thiệu Resonator: Verina</t>
         </is>
       </c>
       <c r="N155" t="inlineStr">
@@ -11354,7 +11354,7 @@
       </c>
       <c r="M156" t="inlineStr">
         <is>
-          <t>Resonator Introduction: Verina</t>
+          <t>Giới Thiệu Resonator: Verina</t>
         </is>
       </c>
       <c r="N156" t="inlineStr">
@@ -11424,7 +11424,7 @@
       </c>
       <c r="M157" t="inlineStr">
         <is>
-          <t>Basic Attack Tutorial: Verina</t>
+          <t>Hướng Dẫn Đòn Cơ Bản: Verina</t>
         </is>
       </c>
       <c r="N157" t="inlineStr">
@@ -11494,7 +11494,7 @@
       </c>
       <c r="M158" t="inlineStr">
         <is>
-          <t>Basic Attack Tutorial: Verina</t>
+          <t>Hướng Dẫn Đòn Cơ Bản: Verina</t>
         </is>
       </c>
       <c r="N158" t="inlineStr">
@@ -11564,7 +11564,7 @@
       </c>
       <c r="M159" t="inlineStr">
         <is>
-          <t>Basic Attack Tutorial: Verina</t>
+          <t>Hướng Dẫn Đòn Cơ Bản: Verina</t>
         </is>
       </c>
       <c r="N159" t="inlineStr">
@@ -11634,7 +11634,7 @@
       </c>
       <c r="M160" t="inlineStr">
         <is>
-          <t>Skill Tutorial: Verina</t>
+          <t>Hướng Dẫn Kỹ Năng: Verina</t>
         </is>
       </c>
       <c r="N160" t="inlineStr">
@@ -11704,7 +11704,7 @@
       </c>
       <c r="M161" t="inlineStr">
         <is>
-          <t>Skill Tutorial: Verina</t>
+          <t>Hướng Dẫn Kỹ Năng: Verina</t>
         </is>
       </c>
       <c r="N161" t="inlineStr">
@@ -11774,7 +11774,7 @@
       </c>
       <c r="M162" t="inlineStr">
         <is>
-          <t>Skill Tutorial: Verina</t>
+          <t>Hướng Dẫn Kỹ Năng: Verina</t>
         </is>
       </c>
       <c r="N162" t="inlineStr">
@@ -11844,7 +11844,7 @@
       </c>
       <c r="M163" t="inlineStr">
         <is>
-          <t>Đội Comp Tutorial: Verina</t>
+          <t>Hướng dẫn Đội Hình: Verina</t>
         </is>
       </c>
       <c r="N163" t="inlineStr">
@@ -11914,7 +11914,7 @@
       </c>
       <c r="M164" t="inlineStr">
         <is>
-          <t>Đội Comp Tutorial: Verina</t>
+          <t>Hướng dẫn Đội Hình: Verina</t>
         </is>
       </c>
       <c r="N164" t="inlineStr">
@@ -12054,7 +12054,7 @@
       </c>
       <c r="M166" t="inlineStr">
         <is>
-          <t>Character Introduction - Yangyang</t>
+          <t>Giới thiệu Nhân vật - Yangyang</t>
         </is>
       </c>
       <c r="N166" t="inlineStr">
@@ -12124,7 +12124,7 @@
       </c>
       <c r="M167" t="inlineStr">
         <is>
-          <t>Character Introduction - Yangyang</t>
+          <t>Giới thiệu Nhân vật - Yangyang</t>
         </is>
       </c>
       <c r="N167" t="inlineStr">
@@ -12194,7 +12194,7 @@
       </c>
       <c r="M168" t="inlineStr">
         <is>
-          <t>Character Introduction - Yangyang</t>
+          <t>Giới thiệu Nhân vật - Yangyang</t>
         </is>
       </c>
       <c r="N168" t="inlineStr">
@@ -12264,7 +12264,7 @@
       </c>
       <c r="M169" t="inlineStr">
         <is>
-          <t>Basic Attack Tutorial - Yangyang</t>
+          <t>Hướng Dẫn Đòn Cơ Bản - Yangyang</t>
         </is>
       </c>
       <c r="N169" t="inlineStr">
@@ -12334,7 +12334,7 @@
       </c>
       <c r="M170" t="inlineStr">
         <is>
-          <t>Skill Tutorial - Yangyang</t>
+          <t>Hướng Dẫn Kỹ Năng - Yangyang</t>
         </is>
       </c>
       <c r="N170" t="inlineStr">
@@ -12404,7 +12404,7 @@
       </c>
       <c r="M171" t="inlineStr">
         <is>
-          <t>Skill Tutorial: Yangyang</t>
+          <t>Hướng Dẫn Kỹ Năng: Yangyang</t>
         </is>
       </c>
       <c r="N171" t="inlineStr">
@@ -12474,7 +12474,7 @@
       </c>
       <c r="M172" t="inlineStr">
         <is>
-          <t>Đội-up Comprehensive Tutorial - Yangyang</t>
+          <t>Hướng dẫn Toàn diện Hợp Tác - Yangyang</t>
         </is>
       </c>
       <c r="N172" t="inlineStr">
@@ -12544,7 +12544,7 @@
       </c>
       <c r="M173" t="inlineStr">
         <is>
-          <t>Đội-up Comprehensive Tutorial - Yangyang</t>
+          <t>Hướng dẫn Toàn diện Hợp Tác - Yangyang</t>
         </is>
       </c>
       <c r="N173" t="inlineStr">
@@ -12684,7 +12684,7 @@
       </c>
       <c r="M175" t="inlineStr">
         <is>
-          <t>Cubie Derby: Warmup</t>
+          <t>Giải Đua Cubie: Khởi Động</t>
         </is>
       </c>
       <c r="N175" t="inlineStr">
@@ -12754,7 +12754,7 @@
       </c>
       <c r="M176" t="inlineStr">
         <is>
-          <t>Cubie Derby: Warmup</t>
+          <t>Giải Đua Cubie: Khởi Động</t>
         </is>
       </c>
       <c r="N176" t="inlineStr">
@@ -12824,7 +12824,7 @@
       </c>
       <c r="M177" t="inlineStr">
         <is>
-          <t>Du ký Ký ức</t>
+          <t>Biên Niên Ký Ức</t>
         </is>
       </c>
       <c r="N177" t="inlineStr">
@@ -12894,7 +12894,7 @@
       </c>
       <c r="M178" t="inlineStr">
         <is>
-          <t>Quà tặng Đại團 viên</t>
+          <t>Mộng Đại Hội Ngộ</t>
         </is>
       </c>
       <c r="N178" t="inlineStr">
@@ -12964,7 +12964,7 @@
       </c>
       <c r="M179" t="inlineStr">
         <is>
-          <t>Quà tặng Khúc ca Du dương</t>
+          <t>Quà Tặng Khúc Ca Du Dương</t>
         </is>
       </c>
       <c r="N179" t="inlineStr">
@@ -13034,7 +13034,7 @@
       </c>
       <c r="M180" t="inlineStr">
         <is>
-          <t>Vượt Sóng: Rinascita</t>
+          <t>Vượt Qua Những Con Sóng: Rinascita</t>
         </is>
       </c>
       <c r="N180" t="inlineStr">
@@ -13104,7 +13104,7 @@
       </c>
       <c r="M181" t="inlineStr">
         <is>
-          <t>Quà tặng Đại lễ hội</t>
+          <t>Mộng Đại Lễ</t>
         </is>
       </c>
       <c r="N181" t="inlineStr">
@@ -13174,7 +13174,7 @@
       </c>
       <c r="M182" t="inlineStr">
         <is>
-          <t>Podcast Pioneer</t>
+          <t>Podcast Tiên Phong</t>
         </is>
       </c>
       <c r="N182" t="inlineStr">
@@ -13244,7 +13244,7 @@
       </c>
       <c r="M183" t="inlineStr">
         <is>
-          <t>Liên hoan phim Solaris</t>
+          <t>Liên hoan Điện ảnh Solaris</t>
         </is>
       </c>
       <c r="N183" t="inlineStr">
@@ -13314,7 +13314,7 @@
       </c>
       <c r="M184" t="inlineStr">
         <is>
-          <t>Pioneer Association Commissions</t>
+          <t>Nhiệm Vụ của Hiệp Hội Tiên Phong</t>
         </is>
       </c>
       <c r="N184" t="inlineStr">
@@ -13384,7 +13384,7 @@
       </c>
       <c r="M185" t="inlineStr">
         <is>
-          <t>Trial Resonators</t>
+          <t>Resonator Thử Nghiệm</t>
         </is>
       </c>
       <c r="N185" t="inlineStr">
@@ -13454,7 +13454,7 @@
       </c>
       <c r="M186" t="inlineStr">
         <is>
-          <t>Sổ tay</t>
+          <t>Sổ Hướng Dẫn</t>
         </is>
       </c>
       <c r="N186" t="inlineStr">
@@ -13524,7 +13524,7 @@
       </c>
       <c r="M187" t="inlineStr">
         <is>
-          <t>Sổ tay</t>
+          <t>Sổ Hướng Dẫn</t>
         </is>
       </c>
       <c r="N187" t="inlineStr">
@@ -13594,7 +13594,7 @@
       </c>
       <c r="M188" t="inlineStr">
         <is>
-          <t>Theo dấu Kẻ địch</t>
+          <t>Theo Dõi Kẻ Địch</t>
         </is>
       </c>
       <c r="N188" t="inlineStr">
@@ -13734,7 +13734,7 @@
       </c>
       <c r="M190" t="inlineStr">
         <is>
-          <t>Chiến dịch Lollo: Xác minh</t>
+          <t>Chiến Dịch Lollo: Xác Minh</t>
         </is>
       </c>
       <c r="N190" t="inlineStr">
@@ -14084,7 +14084,7 @@
       </c>
       <c r="M195" t="inlineStr">
         <is>
-          <t>Resonators</t>
+          <t>Resonator</t>
         </is>
       </c>
       <c r="N195" t="inlineStr">
@@ -14154,7 +14154,7 @@
       </c>
       <c r="M196" t="inlineStr">
         <is>
-          <t>Activity Points Introduction</t>
+          <t>Giới Thiệu Điểm Hoạt Động</t>
         </is>
       </c>
       <c r="N196" t="inlineStr">
@@ -14224,7 +14224,7 @@
       </c>
       <c r="M197" t="inlineStr">
         <is>
-          <t>"Banners Never Fall" Challenges</t>
+          <t>"Thử Thách 'Cờ Không Bại'"</t>
         </is>
       </c>
       <c r="N197" t="inlineStr">
@@ -14294,7 +14294,7 @@
       </c>
       <c r="M198" t="inlineStr">
         <is>
-          <t>"Banners Never Fall" Challenges</t>
+          <t>"Thử Thách 'Cờ Không Bại'"</t>
         </is>
       </c>
       <c r="N198" t="inlineStr">
@@ -14504,7 +14504,7 @@
       </c>
       <c r="M201" t="inlineStr">
         <is>
-          <t>Event Conclusion</t>
+          <t>Kết thúc sự kiện</t>
         </is>
       </c>
       <c r="N201" t="inlineStr">
@@ -14574,7 +14574,7 @@
       </c>
       <c r="M202" t="inlineStr">
         <is>
-          <t>Thử nghiệm/Nội dung Thử thách Vật liệu</t>
+          <t>Nội dung Thử Thách Vật Phẩm</t>
         </is>
       </c>
       <c r="N202" t="inlineStr">
@@ -14644,7 +14644,7 @@
       </c>
       <c r="M203" t="inlineStr">
         <is>
-          <t>Thử nghiệm/Thử thách Vật liệu</t>
+          <t>test/Thử Thách Nguyên Liệu</t>
         </is>
       </c>
       <c r="N203" t="inlineStr">
@@ -14714,7 +14714,7 @@
       </c>
       <c r="M204" t="inlineStr">
         <is>
-          <t>Giới thiệu về Sự kiện</t>
+          <t>Về Sự Kiện</t>
         </is>
       </c>
       <c r="N204" t="inlineStr">
@@ -14854,7 +14854,7 @@
       </c>
       <c r="M206" t="inlineStr">
         <is>
-          <t>Phần thưởng Giới hạn Thời gian</t>
+          <t>Các Phần Thưởng Giới Hạn</t>
         </is>
       </c>
       <c r="N206" t="inlineStr">
@@ -14924,7 +14924,7 @@
       </c>
       <c r="M207" t="inlineStr">
         <is>
-          <t>Đỉnh cao Danh vọng</t>
+          <t>Đỉnh Cao Danh Vọng</t>
         </is>
       </c>
       <c r="N207" t="inlineStr">
@@ -14994,7 +14994,7 @@
       </c>
       <c r="M208" t="inlineStr">
         <is>
-          <t>Echoes</t>
+          <t>Echo</t>
         </is>
       </c>
       <c r="N208" t="inlineStr">
@@ -15064,7 +15064,7 @@
       </c>
       <c r="M209" t="inlineStr">
         <is>
-          <t>Chiến thuật</t>
+          <t>Chiến Thuật</t>
         </is>
       </c>
       <c r="N209" t="inlineStr">
@@ -15134,7 +15134,7 @@
       </c>
       <c r="M210" t="inlineStr">
         <is>
-          <t>Bộ Sưu Tập Echo</t>
+          <t>Thu Thập Tiếng Vọng</t>
         </is>
       </c>
       <c r="N210" t="inlineStr">
@@ -15344,7 +15344,7 @@
       </c>
       <c r="M213" t="inlineStr">
         <is>
-          <t>Cấp độ Duelist</t>
+          <t>Cấp Độ Đấu Sĩ</t>
         </is>
       </c>
       <c r="N213" t="inlineStr">
@@ -15484,7 +15484,7 @@
       </c>
       <c r="M215" t="inlineStr">
         <is>
-          <t>Dấu Chân Cao Nguyên</t>
+          <t>Dấu Vết Cao Nguyên</t>
         </is>
       </c>
       <c r="N215" t="inlineStr">
@@ -15624,7 +15624,7 @@
       </c>
       <c r="M217" t="inlineStr">
         <is>
-          <t>Săn đuổi Tro và Thép</t>
+          <t>Cuộc săn tro tàn và thép lạnh</t>
         </is>
       </c>
       <c r="N217" t="inlineStr">
@@ -15694,7 +15694,7 @@
       </c>
       <c r="M218" t="inlineStr">
         <is>
-          <t>Trạm Chiến thuật</t>
+          <t>Thiết Bị Chiến Thuật</t>
         </is>
       </c>
       <c r="N218" t="inlineStr">
@@ -15764,7 +15764,7 @@
       </c>
       <c r="M219" t="inlineStr">
         <is>
-          <t>Tổng Quan Tacet Discords</t>
+          <t>Tổng quan Tacet Discord</t>
         </is>
       </c>
       <c r="N219" t="inlineStr">
@@ -15834,7 +15834,7 @@
       </c>
       <c r="M220" t="inlineStr">
         <is>
-          <t>Mô phỏng Phòng thủ Thủy triều</t>
+          <t>Mô Phỏng Phòng Thủ Thủy Triều</t>
         </is>
       </c>
       <c r="N220" t="inlineStr">
@@ -15904,7 +15904,7 @@
       </c>
       <c r="M221" t="inlineStr">
         <is>
-          <t>Save Feature</t>
+          <t>Lưu Tính Năng</t>
         </is>
       </c>
       <c r="N221" t="inlineStr">
@@ -15974,7 +15974,7 @@
       </c>
       <c r="M222" t="inlineStr">
         <is>
-          <t>Dự án Windrider</t>
+          <t>Dự Án Kỵ Sĩ Gió</t>
         </is>
       </c>
       <c r="N222" t="inlineStr">
@@ -16044,7 +16044,7 @@
       </c>
       <c r="M223" t="inlineStr">
         <is>
-          <t>Sanguis Plateaus Travel Atlas</t>
+          <t>Bản Đồ Du Hành Cao Nguyên Sanguis</t>
         </is>
       </c>
       <c r="N223" t="inlineStr">
@@ -16184,7 +16184,7 @@
       </c>
       <c r="M225" t="inlineStr">
         <is>
-          <t>Moonlit Revelation</t>
+          <t>Bí Ẩn Dưới Trăng</t>
         </is>
       </c>
       <c r="N225" t="inlineStr">
@@ -16324,7 +16324,7 @@
       </c>
       <c r="M227" t="inlineStr">
         <is>
-          <t>Casket Sonar</t>
+          <t>Siêu Âm Quan Tài</t>
         </is>
       </c>
       <c r="N227" t="inlineStr">
@@ -16394,7 +16394,7 @@
       </c>
       <c r="M228" t="inlineStr">
         <is>
-          <t>Freeze Frame: Những Khoảnh Khắc Nổi Bật</t>
+          <t>Định Hình: Điểm Nổi Bật Hành Động</t>
         </is>
       </c>
       <c r="N228" t="inlineStr">
@@ -16464,7 +16464,7 @@
       </c>
       <c r="M229" t="inlineStr">
         <is>
-          <t>Lootmapper</t>
+          <t>Bản Đồ Tài Nguyên</t>
         </is>
       </c>
       <c r="N229" t="inlineStr">
@@ -16534,7 +16534,7 @@
       </c>
       <c r="M230" t="inlineStr">
         <is>
-          <t>Waypoint</t>
+          <t>Điểm Dẫn Đường</t>
         </is>
       </c>
       <c r="N230" t="inlineStr">
@@ -16604,7 +16604,7 @@
       </c>
       <c r="M231" t="inlineStr">
         <is>
-          <t>Resonators</t>
+          <t>Resonator</t>
         </is>
       </c>
       <c r="N231" t="inlineStr">
@@ -16674,7 +16674,7 @@
       </c>
       <c r="M232" t="inlineStr">
         <is>
-          <t>Lời thì thầm của sóng</t>
+          <t>Lời thì thầm của sóng biển</t>
         </is>
       </c>
       <c r="N232" t="inlineStr">
@@ -16744,7 +16744,7 @@
       </c>
       <c r="M233" t="inlineStr">
         <is>
-          <t>Quà tặng Hổ phách</t>
+          <t>Quà tặng Hổ Phách</t>
         </is>
       </c>
       <c r="N233" t="inlineStr">
@@ -16814,7 +16814,7 @@
       </c>
       <c r="M234" t="inlineStr">
         <is>
-          <t>Quà tặng Khúc ca Mực tím</t>
+          <t>Mộng Khúc Ca Mực Tàu</t>
         </is>
       </c>
       <c r="N234" t="inlineStr">
@@ -16954,7 +16954,7 @@
       </c>
       <c r="M236" t="inlineStr">
         <is>
-          <t>Echo Hệ thống</t>
+          <t>Hệ Thống Tiếng Vọng</t>
         </is>
       </c>
       <c r="N236" t="inlineStr">
@@ -17024,7 +17024,7 @@
       </c>
       <c r="M237" t="inlineStr">
         <is>
-          <t>Echo Build</t>
+          <t>Cấu Hình Echo</t>
         </is>
       </c>
       <c r="N237" t="inlineStr">
@@ -17234,7 +17234,7 @@
       </c>
       <c r="M240" t="inlineStr">
         <is>
-          <t>Vực Sâu Cõi Ảo Ảnh</t>
+          <t>Vực Sâu Cõi Ảo</t>
         </is>
       </c>
       <c r="N240" t="inlineStr">
@@ -17304,7 +17304,7 @@
       </c>
       <c r="M241" t="inlineStr">
         <is>
-          <t>Somnoire Collection Hệ thống</t>
+          <t>Hệ Thống Thu Thập Somnoire</t>
         </is>
       </c>
       <c r="N241" t="inlineStr">
@@ -17374,7 +17374,7 @@
       </c>
       <c r="M242" t="inlineStr">
         <is>
-          <t>Somnoire Collection Hệ thống</t>
+          <t>Hệ Thống Thu Thập Somnoire</t>
         </is>
       </c>
       <c r="N242" t="inlineStr">
@@ -17444,7 +17444,7 @@
       </c>
       <c r="M243" t="inlineStr">
         <is>
-          <t>Overdash Club</t>
+          <t>Câu lạc bộ Bay vượt tốc</t>
         </is>
       </c>
       <c r="N243" t="inlineStr">
@@ -17514,7 +17514,7 @@
       </c>
       <c r="M244" t="inlineStr">
         <is>
-          <t>Bộ Sưu Tập Echo</t>
+          <t>Thu Thập Tiếng Vọng</t>
         </is>
       </c>
       <c r="N244" t="inlineStr">
@@ -17584,7 +17584,7 @@
       </c>
       <c r="M245" t="inlineStr">
         <is>
-          <t>Ngân hàng dữ liệu</t>
+          <t>Ngân Hàng Dữ Liệu</t>
         </is>
       </c>
       <c r="N245" t="inlineStr">
@@ -17654,7 +17654,7 @@
       </c>
       <c r="M246" t="inlineStr">
         <is>
-          <t>Trò Chơi Thẻ</t>
+          <t>Trò chơi Thẻ</t>
         </is>
       </c>
       <c r="N246" t="inlineStr">
@@ -17794,7 +17794,7 @@
       </c>
       <c r="M248" t="inlineStr">
         <is>
-          <t>Forever Fest Vibe Gauge</t>
+          <t>Đồng Hồ Sắc Thái Lễ Hội Vĩnh Hằng</t>
         </is>
       </c>
       <c r="N248" t="inlineStr">
@@ -17864,7 +17864,7 @@
       </c>
       <c r="M249" t="inlineStr">
         <is>
-          <t>Weapon Display Stands</t>
+          <t>Giá Trưng Bày Vũ Khí</t>
         </is>
       </c>
       <c r="N249" t="inlineStr">
@@ -17934,7 +17934,7 @@
       </c>
       <c r="M250" t="inlineStr">
         <is>
-          <t>Echo Display Stands</t>
+          <t>Các Giá Trưng Bày Tiếng Vọng</t>
         </is>
       </c>
       <c r="N250" t="inlineStr">
@@ -18004,7 +18004,7 @@
       </c>
       <c r="M251" t="inlineStr">
         <is>
-          <t>Trang trí tiệc</t>
+          <t>Trang trí nhóm</t>
         </is>
       </c>
       <c r="N251" t="inlineStr">
@@ -18074,7 +18074,7 @@
       </c>
       <c r="M252" t="inlineStr">
         <is>
-          <t>Nâng cấp Cấp Độ Union</t>
+          <t>Nâng cấp Cấp Liên Minh</t>
         </is>
       </c>
       <c r="N252" t="inlineStr">
@@ -18144,7 +18144,7 @@
       </c>
       <c r="M253" t="inlineStr">
         <is>
-          <t>Túi đồ Interface</t>
+          <t>Giao diện Túi đồ</t>
         </is>
       </c>
       <c r="N253" t="inlineStr">
@@ -18214,7 +18214,7 @@
       </c>
       <c r="M254" t="inlineStr">
         <is>
-          <t>Nơi Các Vì Sao Rơi Xuống</t>
+          <t>Nơi Sao Rơi Như Mưa</t>
         </is>
       </c>
       <c r="N254" t="inlineStr">
@@ -18284,7 +18284,7 @@
       </c>
       <c r="M255" t="inlineStr">
         <is>
-          <t>Phần thưởng Giới hạn Thời gian của Where Stars Cascade Down</t>
+          <t>Phần Thưởng Giới Hạn Của Nơi Sao Rơi</t>
         </is>
       </c>
       <c r="N255" t="inlineStr">
@@ -18354,7 +18354,7 @@
       </c>
       <c r="M256" t="inlineStr">
         <is>
-          <t>Quà tặng Sương tan</t>
+          <t>Quà Tặng Sương Tan</t>
         </is>
       </c>
       <c r="N256" t="inlineStr">
@@ -18424,7 +18424,7 @@
       </c>
       <c r="M257" t="inlineStr">
         <is>
-          <t>Thẻ Ngẫu nhiên</t>
+          <t>Quân Bài Bất Ngờ</t>
         </is>
       </c>
       <c r="N257" t="inlineStr">
@@ -18494,7 +18494,7 @@
       </c>
       <c r="M258" t="inlineStr">
         <is>
-          <t>Vực Sâu Cõi Ảo Ảnh</t>
+          <t>Vực Sâu Cõi Ảo</t>
         </is>
       </c>
       <c r="N258" t="inlineStr">
@@ -18564,7 +18564,7 @@
       </c>
       <c r="M259" t="inlineStr">
         <is>
-          <t>Awakening Journey</t>
+          <t>Hành Trình Thức Tỉnh</t>
         </is>
       </c>
       <c r="N259" t="inlineStr">
@@ -18634,7 +18634,7 @@
       </c>
       <c r="M260" t="inlineStr">
         <is>
-          <t>Voyage's Beginning</t>
+          <t>Khởi Đầu Hành Trình</t>
         </is>
       </c>
       <c r="N260" t="inlineStr">
@@ -18704,7 +18704,7 @@
       </c>
       <c r="M261" t="inlineStr">
         <is>
-          <t>Rumbling Hollows</t>
+          <t>Hố Sóng Âm</t>
         </is>
       </c>
       <c r="N261" t="inlineStr">
@@ -18774,7 +18774,7 @@
       </c>
       <c r="M262" t="inlineStr">
         <is>
-          <t>Terminal EXP</t>
+          <t>Điểm Kinh Nghiệm Thiết Bị Đầu Cuối</t>
         </is>
       </c>
       <c r="N262" t="inlineStr">
@@ -18844,7 +18844,7 @@
       </c>
       <c r="M263" t="inlineStr">
         <is>
-          <t>Character Introduction: Taoqi</t>
+          <t>Giới thiệu Nhân vật: Taoqi</t>
         </is>
       </c>
       <c r="N263" t="inlineStr">
@@ -18914,7 +18914,7 @@
       </c>
       <c r="M264" t="inlineStr">
         <is>
-          <t>Character Introduction: Taoqi</t>
+          <t>Giới thiệu Nhân vật: Taoqi</t>
         </is>
       </c>
       <c r="N264" t="inlineStr">
@@ -18984,7 +18984,7 @@
       </c>
       <c r="M265" t="inlineStr">
         <is>
-          <t>Character Introduction: Taoqi</t>
+          <t>Giới thiệu Nhân vật: Taoqi</t>
         </is>
       </c>
       <c r="N265" t="inlineStr">
@@ -19054,7 +19054,7 @@
       </c>
       <c r="M266" t="inlineStr">
         <is>
-          <t>Character Introduction: Taoqi</t>
+          <t>Giới thiệu Nhân vật: Taoqi</t>
         </is>
       </c>
       <c r="N266" t="inlineStr">
@@ -19124,7 +19124,7 @@
       </c>
       <c r="M267" t="inlineStr">
         <is>
-          <t>Birthday Blessing Feature</t>
+          <t>Tính Năng Chúc Mừng Sinh Nhật</t>
         </is>
       </c>
       <c r="N267" t="inlineStr">
@@ -19194,7 +19194,7 @@
       </c>
       <c r="M268" t="inlineStr">
         <is>
-          <t>Absorb Echo</t>
+          <t>Hấp thụ Echo</t>
         </is>
       </c>
       <c r="N268" t="inlineStr">
@@ -19334,7 +19334,7 @@
       </c>
       <c r="M270" t="inlineStr">
         <is>
-          <t>Resonance Beacon</t>
+          <t>Điểm Cộng Hưởng</t>
         </is>
       </c>
       <c r="N270" t="inlineStr">
@@ -19404,7 +19404,7 @@
       </c>
       <c r="M271" t="inlineStr">
         <is>
-          <t>Sonance Casket</t>
+          <t>Hòm Thanh Âm</t>
         </is>
       </c>
       <c r="N271" t="inlineStr">
@@ -19474,7 +19474,7 @@
       </c>
       <c r="M272" t="inlineStr">
         <is>
-          <t>Synthesis</t>
+          <t>Tổng Hợp</t>
         </is>
       </c>
       <c r="N272" t="inlineStr">
@@ -19544,7 +19544,7 @@
       </c>
       <c r="M273" t="inlineStr">
         <is>
-          <t>Recovery</t>
+          <t>Hồi phục</t>
         </is>
       </c>
       <c r="N273" t="inlineStr">
@@ -19614,7 +19614,7 @@
       </c>
       <c r="M274" t="inlineStr">
         <is>
-          <t>Area Information</t>
+          <t>Thông tin khu vực</t>
         </is>
       </c>
       <c r="N274" t="inlineStr">
@@ -19684,7 +19684,7 @@
       </c>
       <c r="M275" t="inlineStr">
         <is>
-          <t>Vibration Strength</t>
+          <t>Cường Độ Rung Động</t>
         </is>
       </c>
       <c r="N275" t="inlineStr">
@@ -19754,7 +19754,7 @@
       </c>
       <c r="M276" t="inlineStr">
         <is>
-          <t>Counterattack</t>
+          <t>Phản công</t>
         </is>
       </c>
       <c r="N276" t="inlineStr">
@@ -19824,7 +19824,7 @@
       </c>
       <c r="M277" t="inlineStr">
         <is>
-          <t>Dodge</t>
+          <t>Né tránh</t>
         </is>
       </c>
       <c r="N277" t="inlineStr">
@@ -19894,7 +19894,7 @@
       </c>
       <c r="M278" t="inlineStr">
         <is>
-          <t>Finishing Attack</t>
+          <t>Đòn Kết Thúc</t>
         </is>
       </c>
       <c r="N278" t="inlineStr">
@@ -19964,7 +19964,7 @@
       </c>
       <c r="M279" t="inlineStr">
         <is>
-          <t>Immobilize</t>
+          <t>Hóa Bất Động</t>
         </is>
       </c>
       <c r="N279" t="inlineStr">
@@ -20034,7 +20034,7 @@
       </c>
       <c r="M280" t="inlineStr">
         <is>
-          <t>Điểm Treo Móc</t>
+          <t>Điểm Neo Bám</t>
         </is>
       </c>
       <c r="N280" t="inlineStr">
@@ -20104,7 +20104,7 @@
       </c>
       <c r="M281" t="inlineStr">
         <is>
-          <t>Grapple</t>
+          <t>Móc Câu</t>
         </is>
       </c>
       <c r="N281" t="inlineStr">
@@ -20244,7 +20244,7 @@
       </c>
       <c r="M283" t="inlineStr">
         <is>
-          <t>Sensor</t>
+          <t>Cảm Biến</t>
         </is>
       </c>
       <c r="N283" t="inlineStr">
@@ -20314,7 +20314,7 @@
       </c>
       <c r="M284" t="inlineStr">
         <is>
-          <t>Công cụ</t>
+          <t>Tiện ích</t>
         </is>
       </c>
       <c r="N284" t="inlineStr">
@@ -20384,7 +20384,7 @@
       </c>
       <c r="M285" t="inlineStr">
         <is>
-          <t>Công cụ</t>
+          <t>Tiện ích</t>
         </is>
       </c>
       <c r="N285" t="inlineStr">
@@ -20454,7 +20454,7 @@
       </c>
       <c r="M286" t="inlineStr">
         <is>
-          <t>Outro Skill &amp; Intro Skill</t>
+          <t>Kỹ Năng Hồi Kết &amp; Kỹ Năng Khai Chiến</t>
         </is>
       </c>
       <c r="N286" t="inlineStr">
@@ -20594,7 +20594,7 @@
       </c>
       <c r="M288" t="inlineStr">
         <is>
-          <t>Kinh Nghiệm Liên Minh &amp; Cấp Độ Liên Minh</t>
+          <t>Kinh nghiệm &amp; Cấp Liên Minh</t>
         </is>
       </c>
       <c r="N288" t="inlineStr">
@@ -20664,7 +20664,7 @@
       </c>
       <c r="M289" t="inlineStr">
         <is>
-          <t>Kinh Nghiệm Liên Minh &amp; Cấp Độ Liên Minh</t>
+          <t>Kinh nghiệm &amp; Cấp Liên Minh</t>
         </is>
       </c>
       <c r="N289" t="inlineStr">
@@ -20734,7 +20734,7 @@
       </c>
       <c r="M290" t="inlineStr">
         <is>
-          <t>Công cụ</t>
+          <t>Tiện ích</t>
         </is>
       </c>
       <c r="N290" t="inlineStr">
@@ -20804,7 +20804,7 @@
       </c>
       <c r="M291" t="inlineStr">
         <is>
-          <t>Công cụ: Sensor I</t>
+          <t>Tiện ích: Cảm biến I</t>
         </is>
       </c>
       <c r="N291" t="inlineStr">
@@ -20874,7 +20874,7 @@
       </c>
       <c r="M292" t="inlineStr">
         <is>
-          <t>Công cụ: Sensor II</t>
+          <t>Tiện ích: Cảm biến II</t>
         </is>
       </c>
       <c r="N292" t="inlineStr">
@@ -20944,7 +20944,7 @@
       </c>
       <c r="M293" t="inlineStr">
         <is>
-          <t>Công cụ: Grapple</t>
+          <t>Tiện ích: Móc néo</t>
         </is>
       </c>
       <c r="N293" t="inlineStr">
@@ -21014,7 +21014,7 @@
       </c>
       <c r="M294" t="inlineStr">
         <is>
-          <t>Công cụ: Levitator</t>
+          <t>Tiện ích: Bộ nâng bay</t>
         </is>
       </c>
       <c r="N294" t="inlineStr">
@@ -21084,7 +21084,7 @@
       </c>
       <c r="M295" t="inlineStr">
         <is>
-          <t>Di chuyển nhanh</t>
+          <t>Dịch chuyển nhanh</t>
         </is>
       </c>
       <c r="N295" t="inlineStr">
@@ -21154,7 +21154,7 @@
       </c>
       <c r="M296" t="inlineStr">
         <is>
-          <t>Resonance Nexus</t>
+          <t>Mạng Lưới Cộng Hưởng</t>
         </is>
       </c>
       <c r="N296" t="inlineStr">
@@ -21224,7 +21224,7 @@
       </c>
       <c r="M297" t="inlineStr">
         <is>
-          <t>Resonance Nexus: Rally</t>
+          <t>Mạng Lưới Cộng Hưởng: Tập Hợp</t>
         </is>
       </c>
       <c r="N297" t="inlineStr">
@@ -21294,7 +21294,7 @@
       </c>
       <c r="M298" t="inlineStr">
         <is>
-          <t>Rally</t>
+          <t>Tập Hợp</t>
         </is>
       </c>
       <c r="N298" t="inlineStr">
@@ -21364,7 +21364,7 @@
       </c>
       <c r="M299" t="inlineStr">
         <is>
-          <t>Weak Point Attack</t>
+          <t>Tấn Công Điểm Yếu</t>
         </is>
       </c>
       <c r="N299" t="inlineStr">
@@ -21574,7 +21574,7 @@
       </c>
       <c r="M302" t="inlineStr">
         <is>
-          <t>Tacet Field: Phần Thưởng</t>
+          <t>Tổ Tacet: Phần Thưởng</t>
         </is>
       </c>
       <c r="N302" t="inlineStr">
@@ -22624,7 +22624,7 @@
       </c>
       <c r="M317" t="inlineStr">
         <is>
-          <t>Autopuppet Scout</t>
+          <t>Trinh Sát Tự Động</t>
         </is>
       </c>
       <c r="N317" t="inlineStr">
@@ -23114,7 +23114,7 @@
       </c>
       <c r="M324" t="inlineStr">
         <is>
-          <t>Sư Tử Nữ Vinh Quang</t>
+          <t>Sư Tử Vinh Quang - Giai Đoạn Truy Cập Sớm</t>
         </is>
       </c>
       <c r="N324" t="inlineStr">
@@ -23254,7 +23254,7 @@
       </c>
       <c r="M326" t="inlineStr">
         <is>
-          <t>Pilgrim's Shell</t>
+          <t>Vỏ Sò Hành Hương</t>
         </is>
       </c>
       <c r="N326" t="inlineStr">
@@ -23324,7 +23324,7 @@
       </c>
       <c r="M327" t="inlineStr">
         <is>
-          <t>Gladiator</t>
+          <t>Đấu sĩ</t>
         </is>
       </c>
       <c r="N327" t="inlineStr">
@@ -23534,7 +23534,7 @@
       </c>
       <c r="M330" t="inlineStr">
         <is>
-          <t>Tacet Field: Tacetite Bloom</t>
+          <t>Tổ Tacet: Tacetite Nở Hoa</t>
         </is>
       </c>
       <c r="N330" t="inlineStr">
@@ -23674,7 +23674,7 @@
       </c>
       <c r="M332" t="inlineStr">
         <is>
-          <t>Unlocking Echoes</t>
+          <t>Mở khóa Tiếng Vọng</t>
         </is>
       </c>
       <c r="N332" t="inlineStr">
@@ -23744,7 +23744,7 @@
       </c>
       <c r="M333" t="inlineStr">
         <is>
-          <t>Viewing Echoes</t>
+          <t>Xem Dư Âm</t>
         </is>
       </c>
       <c r="N333" t="inlineStr">
@@ -23884,7 +23884,7 @@
       </c>
       <c r="M335" t="inlineStr">
         <is>
-          <t>Duel Resonance</t>
+          <t>Cộng Hưởng Đối Kháng</t>
         </is>
       </c>
       <c r="N335" t="inlineStr">
@@ -23954,7 +23954,7 @@
       </c>
       <c r="M336" t="inlineStr">
         <is>
-          <t>Tacet Field: Interference</t>
+          <t>Tổ Tacet: Vùng nhiễu loạn</t>
         </is>
       </c>
       <c r="N336" t="inlineStr">
@@ -24024,7 +24024,7 @@
       </c>
       <c r="M337" t="inlineStr">
         <is>
-          <t>Corroder</t>
+          <t>Kẻ Ăn Mòn</t>
         </is>
       </c>
       <c r="N337" t="inlineStr">
@@ -24094,7 +24094,7 @@
       </c>
       <c r="M338" t="inlineStr">
         <is>
-          <t>Spikes</t>
+          <t>Gai Nhọn</t>
         </is>
       </c>
       <c r="N338" t="inlineStr">
@@ -24164,7 +24164,7 @@
       </c>
       <c r="M339" t="inlineStr">
         <is>
-          <t>Induction Cell &amp; Cell Socket</t>
+          <t>Pin Cảm Ứng &amp; Đế Pin</t>
         </is>
       </c>
       <c r="N339" t="inlineStr">
@@ -24234,7 +24234,7 @@
       </c>
       <c r="M340" t="inlineStr">
         <is>
-          <t>Induction Cell &amp; Cell Socket</t>
+          <t>Pin Cảm Ứng &amp; Đế Pin</t>
         </is>
       </c>
       <c r="N340" t="inlineStr">
@@ -24304,7 +24304,7 @@
       </c>
       <c r="M341" t="inlineStr">
         <is>
-          <t>Transducer</t>
+          <t>Bộ chuyển đổi</t>
         </is>
       </c>
       <c r="N341" t="inlineStr">
@@ -24374,7 +24374,7 @@
       </c>
       <c r="M342" t="inlineStr">
         <is>
-          <t>Fragile Rock</t>
+          <t>Đá Mỏng Manh</t>
         </is>
       </c>
       <c r="N342" t="inlineStr">
@@ -24444,7 +24444,7 @@
       </c>
       <c r="M343" t="inlineStr">
         <is>
-          <t>Road Sign</t>
+          <t>Biển Chỉ Đường</t>
         </is>
       </c>
       <c r="N343" t="inlineStr">
@@ -24514,7 +24514,7 @@
       </c>
       <c r="M344" t="inlineStr">
         <is>
-          <t>Tactical Hologram: Thử Thách</t>
+          <t>Bản Hologram Chiến Thuật: Thử Thách</t>
         </is>
       </c>
       <c r="N344" t="inlineStr">
@@ -24584,7 +24584,7 @@
       </c>
       <c r="M345" t="inlineStr">
         <is>
-          <t>Sound Emulator</t>
+          <t>Bộ Mô Phỏng Âm Thanh</t>
         </is>
       </c>
       <c r="N345" t="inlineStr">
@@ -24654,7 +24654,7 @@
       </c>
       <c r="M346" t="inlineStr">
         <is>
-          <t>Tactical Hologram: Overdash</t>
+          <t>Hologram Chiến Thuật: Overdash</t>
         </is>
       </c>
       <c r="N346" t="inlineStr">
@@ -24724,7 +24724,7 @@
       </c>
       <c r="M347" t="inlineStr">
         <is>
-          <t>Mô-đun: Speed</t>
+          <t>Mô-đun: Tốc Độ</t>
         </is>
       </c>
       <c r="N347" t="inlineStr">
@@ -24934,7 +24934,7 @@
       </c>
       <c r="M350" t="inlineStr">
         <is>
-          <t>Signals Console</t>
+          <t>Bảng điều khiển Tín hiệu</t>
         </is>
       </c>
       <c r="N350" t="inlineStr">
@@ -25004,7 +25004,7 @@
       </c>
       <c r="M351" t="inlineStr">
         <is>
-          <t>Signals Console</t>
+          <t>Bảng điều khiển Tín hiệu</t>
         </is>
       </c>
       <c r="N351" t="inlineStr">
@@ -25074,7 +25074,7 @@
       </c>
       <c r="M352" t="inlineStr">
         <is>
-          <t>Signals Hub</t>
+          <t>Trung tâm Tín hiệu</t>
         </is>
       </c>
       <c r="N352" t="inlineStr">
@@ -25144,7 +25144,7 @@
       </c>
       <c r="M353" t="inlineStr">
         <is>
-          <t>Pressure Platform</t>
+          <t>Nền Đỡ Áp Lực</t>
         </is>
       </c>
       <c r="N353" t="inlineStr">
@@ -25214,7 +25214,7 @@
       </c>
       <c r="M354" t="inlineStr">
         <is>
-          <t>Locked Circuit</t>
+          <t>Mạch Khóa</t>
         </is>
       </c>
       <c r="N354" t="inlineStr">
@@ -25284,7 +25284,7 @@
       </c>
       <c r="M355" t="inlineStr">
         <is>
-          <t>Pressure Platform</t>
+          <t>Nền Đỡ Áp Lực</t>
         </is>
       </c>
       <c r="N355" t="inlineStr">
@@ -25354,7 +25354,7 @@
       </c>
       <c r="M356" t="inlineStr">
         <is>
-          <t>Energy Matrix: I</t>
+          <t>Ma Trận Năng Lượng: Cấp I</t>
         </is>
       </c>
       <c r="N356" t="inlineStr">
@@ -25424,7 +25424,7 @@
       </c>
       <c r="M357" t="inlineStr">
         <is>
-          <t>Encryption Block: I</t>
+          <t>Khối Mã Hóa: I</t>
         </is>
       </c>
       <c r="N357" t="inlineStr">
@@ -25494,7 +25494,7 @@
       </c>
       <c r="M358" t="inlineStr">
         <is>
-          <t>Grapple Shooter</t>
+          <t>Súng Móc</t>
         </is>
       </c>
       <c r="N358" t="inlineStr">
@@ -25634,7 +25634,7 @@
       </c>
       <c r="M360" t="inlineStr">
         <is>
-          <t>Explosive Charge: I</t>
+          <t>Bom nổ: Cấp I</t>
         </is>
       </c>
       <c r="N360" t="inlineStr">
@@ -25704,7 +25704,7 @@
       </c>
       <c r="M361" t="inlineStr">
         <is>
-          <t>Explosive Charge: II</t>
+          <t>Bom nổ: Cấp II</t>
         </is>
       </c>
       <c r="N361" t="inlineStr">
@@ -25774,7 +25774,7 @@
       </c>
       <c r="M362" t="inlineStr">
         <is>
-          <t>Magnetic Cube: I</t>
+          <t>Khối Từ Tính: I</t>
         </is>
       </c>
       <c r="N362" t="inlineStr">
@@ -25844,7 +25844,7 @@
       </c>
       <c r="M363" t="inlineStr">
         <is>
-          <t>Thử Thách Echo: Cruisewing</t>
+          <t>Thử Thách Tiếng Vọng: Cruisewing</t>
         </is>
       </c>
       <c r="N363" t="inlineStr">
@@ -25914,7 +25914,7 @@
       </c>
       <c r="M364" t="inlineStr">
         <is>
-          <t>Blobfly</t>
+          <t>Ruồi Bóng</t>
         </is>
       </c>
       <c r="N364" t="inlineStr">
@@ -25984,7 +25984,7 @@
       </c>
       <c r="M365" t="inlineStr">
         <is>
-          <t>Gravitation Vortex</t>
+          <t>Xoáy Hấp Dẫn</t>
         </is>
       </c>
       <c r="N365" t="inlineStr">
@@ -26054,7 +26054,7 @@
       </c>
       <c r="M366" t="inlineStr">
         <is>
-          <t>Backflip</t>
+          <t>Lộn người về sau</t>
         </is>
       </c>
       <c r="N366" t="inlineStr">
@@ -26124,7 +26124,7 @@
       </c>
       <c r="M367" t="inlineStr">
         <is>
-          <t>Send Frequency Signal: II</t>
+          <t>Gửi Tín Hiệu Tần Số: II</t>
         </is>
       </c>
       <c r="N367" t="inlineStr">
@@ -26194,7 +26194,7 @@
       </c>
       <c r="M368" t="inlineStr">
         <is>
-          <t>Send Frequency Signal: I</t>
+          <t>Gửi Tín Hiệu Tần Số: I</t>
         </is>
       </c>
       <c r="N368" t="inlineStr">
@@ -26264,7 +26264,7 @@
       </c>
       <c r="M369" t="inlineStr">
         <is>
-          <t>Fragile Surface Rock</t>
+          <t>Đá Bề Mặt Mỏng Manh</t>
         </is>
       </c>
       <c r="N369" t="inlineStr">
@@ -26334,7 +26334,7 @@
       </c>
       <c r="M370" t="inlineStr">
         <is>
-          <t>Control Puppet</t>
+          <t>Điều khiển Bù nhìn</t>
         </is>
       </c>
       <c r="N370" t="inlineStr">
@@ -26404,7 +26404,7 @@
       </c>
       <c r="M371" t="inlineStr">
         <is>
-          <t>Rotate Space</t>
+          <t>Xoay Không Gian</t>
         </is>
       </c>
       <c r="N371" t="inlineStr">
@@ -26474,7 +26474,7 @@
       </c>
       <c r="M372" t="inlineStr">
         <is>
-          <t>Hit Ground Mechanism</t>
+          <t>Cơ chế Đòn Đánh Mặt Đất</t>
         </is>
       </c>
       <c r="N372" t="inlineStr">
@@ -26544,7 +26544,7 @@
       </c>
       <c r="M373" t="inlineStr">
         <is>
-          <t>Spinning Mechanism</t>
+          <t>Cơ Chế Xoay</t>
         </is>
       </c>
       <c r="N373" t="inlineStr">
@@ -26614,7 +26614,7 @@
       </c>
       <c r="M374" t="inlineStr">
         <is>
-          <t>Toxic Fog Concentration</t>
+          <t>Nồng Độ Sương Mù Độc Hại</t>
         </is>
       </c>
       <c r="N374" t="inlineStr">
@@ -26684,7 +26684,7 @@
       </c>
       <c r="M375" t="inlineStr">
         <is>
-          <t>Tactical Hologram: Detonate</t>
+          <t>Bản Hologram Chiến Thuật: Kích Nổ</t>
         </is>
       </c>
       <c r="N375" t="inlineStr">
@@ -26754,7 +26754,7 @@
       </c>
       <c r="M376" t="inlineStr">
         <is>
-          <t>Hologram Token</t>
+          <t>Mã Thông Báo Hologram</t>
         </is>
       </c>
       <c r="N376" t="inlineStr">
@@ -26824,7 +26824,7 @@
       </c>
       <c r="M377" t="inlineStr">
         <is>
-          <t>Overdash Track Modules</t>
+          <t>Mô-đun đường đua Bay vượt tốc</t>
         </is>
       </c>
       <c r="N377" t="inlineStr">
@@ -26894,7 +26894,7 @@
       </c>
       <c r="M378" t="inlineStr">
         <is>
-          <t>Overdash Track</t>
+          <t>Đường đua Bay vượt tốc</t>
         </is>
       </c>
       <c r="N378" t="inlineStr">
@@ -26964,7 +26964,7 @@
       </c>
       <c r="M379" t="inlineStr">
         <is>
-          <t>Signal Decoder</t>
+          <t>Bộ giải mã tín hiệu</t>
         </is>
       </c>
       <c r="N379" t="inlineStr">
@@ -27034,7 +27034,7 @@
       </c>
       <c r="M380" t="inlineStr">
         <is>
-          <t>Signal Decoder</t>
+          <t>Bộ giải mã tín hiệu</t>
         </is>
       </c>
       <c r="N380" t="inlineStr">
@@ -27244,7 +27244,7 @@
       </c>
       <c r="M383" t="inlineStr">
         <is>
-          <t>Competition Objectives</t>
+          <t>Mục Tiêu Thi Đấu</t>
         </is>
       </c>
       <c r="N383" t="inlineStr">
@@ -27314,7 +27314,7 @@
       </c>
       <c r="M384" t="inlineStr">
         <is>
-          <t>Banner of Conquest</t>
+          <t>Ngọn Cờ Chinh Phục</t>
         </is>
       </c>
       <c r="N384" t="inlineStr">
@@ -27384,7 +27384,7 @@
       </c>
       <c r="M385" t="inlineStr">
         <is>
-          <t>Special Banner</t>
+          <t>Banner Đặc Biệt</t>
         </is>
       </c>
       <c r="N385" t="inlineStr">
@@ -27454,7 +27454,7 @@
       </c>
       <c r="M386" t="inlineStr">
         <is>
-          <t>Chiếm Giữ Banner</t>
+          <t>Chiếm Lấy Cờ Hiệu</t>
         </is>
       </c>
       <c r="N386" t="inlineStr">
@@ -27524,7 +27524,7 @@
       </c>
       <c r="M387" t="inlineStr">
         <is>
-          <t>Battle Engagement Points</t>
+          <t>Điểm Tham Chiến</t>
         </is>
       </c>
       <c r="N387" t="inlineStr">
@@ -27594,7 +27594,7 @@
       </c>
       <c r="M388" t="inlineStr">
         <is>
-          <t>Dream Contagion</t>
+          <t>Lây Nhiễm Mộng</t>
         </is>
       </c>
       <c r="N388" t="inlineStr">
@@ -27664,7 +27664,7 @@
       </c>
       <c r="M389" t="inlineStr">
         <is>
-          <t>Dreamscape Node</t>
+          <t>Điểm Cảnh Mộng</t>
         </is>
       </c>
       <c r="N389" t="inlineStr">
@@ -27734,7 +27734,7 @@
       </c>
       <c r="M390" t="inlineStr">
         <is>
-          <t>Dream Contagion: Kerasaur</t>
+          <t>Ác Mộng Truyền Nhiễm: Kerasaur</t>
         </is>
       </c>
       <c r="N390" t="inlineStr">
@@ -27804,7 +27804,7 @@
       </c>
       <c r="M391" t="inlineStr">
         <is>
-          <t>Dream Contagion: Drakes</t>
+          <t>Ác Mộng Truyền Nhiễm: Drakes</t>
         </is>
       </c>
       <c r="N391" t="inlineStr">
@@ -27874,7 +27874,7 @@
       </c>
       <c r="M392" t="inlineStr">
         <is>
-          <t>Dream Contagion: Gladiators</t>
+          <t>Ác Mộng Truyền Nhiễm: Gladiators</t>
         </is>
       </c>
       <c r="N392" t="inlineStr">
@@ -27944,7 +27944,7 @@
       </c>
       <c r="M393" t="inlineStr">
         <is>
-          <t>Dream Contagion: Pilgrim's Shell</t>
+          <t>Ác Mộng Truyền Nhiễm: Vỏ Hành Hương</t>
         </is>
       </c>
       <c r="N393" t="inlineStr">
@@ -28014,7 +28014,7 @@
       </c>
       <c r="M394" t="inlineStr">
         <is>
-          <t>Destroying Tidal Blight</t>
+          <t>Đang tiêu diệt Tidal Blight</t>
         </is>
       </c>
       <c r="N394" t="inlineStr">
@@ -28084,7 +28084,7 @@
       </c>
       <c r="M395" t="inlineStr">
         <is>
-          <t>Septimont Patrol Unit</t>
+          <t>Đơn Vị Tuần Tra Septimont</t>
         </is>
       </c>
       <c r="N395" t="inlineStr">
@@ -28154,7 +28154,7 @@
       </c>
       <c r="M396" t="inlineStr">
         <is>
-          <t>Hero's Slash II</t>
+          <t>Thái Anh Hùng II</t>
         </is>
       </c>
       <c r="N396" t="inlineStr">
@@ -28224,7 +28224,7 @@
       </c>
       <c r="M397" t="inlineStr">
         <is>
-          <t>Hero's Slash</t>
+          <t>Thái Anh Hùng</t>
         </is>
       </c>
       <c r="N397" t="inlineStr">
@@ -28294,7 +28294,7 @@
       </c>
       <c r="M398" t="inlineStr">
         <is>
-          <t>Hero's Rend II</t>
+          <t>Phách Anh Hùng II</t>
         </is>
       </c>
       <c r="N398" t="inlineStr">
@@ -28364,7 +28364,7 @@
       </c>
       <c r="M399" t="inlineStr">
         <is>
-          <t>Hero's Rend I</t>
+          <t>Phách Anh Hùng I</t>
         </is>
       </c>
       <c r="N399" t="inlineStr">
@@ -28434,7 +28434,7 @@
       </c>
       <c r="M400" t="inlineStr">
         <is>
-          <t>Bitter Resentment II</t>
+          <t>Oán Hận Đắng Cay II</t>
         </is>
       </c>
       <c r="N400" t="inlineStr">
@@ -28504,7 +28504,7 @@
       </c>
       <c r="M401" t="inlineStr">
         <is>
-          <t>Bitter Resentment II</t>
+          <t>Oán Hận Đắng Cay II</t>
         </is>
       </c>
       <c r="N401" t="inlineStr">
@@ -28574,7 +28574,7 @@
       </c>
       <c r="M402" t="inlineStr">
         <is>
-          <t>Speedrail: Collecting Points</t>
+          <t>Đường Ray Tốc Độ: Thu thập điểm</t>
         </is>
       </c>
       <c r="N402" t="inlineStr">
@@ -28644,7 +28644,7 @@
       </c>
       <c r="M403" t="inlineStr">
         <is>
-          <t>Speedrail: Switching Rails</t>
+          <t>Đường Ray Tốc Độ: Chuyển Ray</t>
         </is>
       </c>
       <c r="N403" t="inlineStr">
@@ -28714,7 +28714,7 @@
       </c>
       <c r="M404" t="inlineStr">
         <is>
-          <t>Vitreum Dancer: Slowdown</t>
+          <t>Vũ Công Pha Lê: Slowdown</t>
         </is>
       </c>
       <c r="N404" t="inlineStr">
@@ -28784,7 +28784,7 @@
       </c>
       <c r="M405" t="inlineStr">
         <is>
-          <t>Hero's Impact: Slash</t>
+          <t>Tác Động Anh Hùng: Vết Chém</t>
         </is>
       </c>
       <c r="N405" t="inlineStr">
@@ -28854,7 +28854,7 @@
       </c>
       <c r="M406" t="inlineStr">
         <is>
-          <t>Hero's Impact: Precision Slash</t>
+          <t>Tác Động Anh Hùng: Vết Chém Chính Xác</t>
         </is>
       </c>
       <c r="N406" t="inlineStr">
@@ -28924,7 +28924,7 @@
       </c>
       <c r="M407" t="inlineStr">
         <is>
-          <t>Ta-da's Protection: Speed Hooray</t>
+          <t>Bảo Vệ Của Ta-da: Nhanh Tay Hoan Hô</t>
         </is>
       </c>
       <c r="N407" t="inlineStr">
@@ -28994,7 +28994,7 @@
       </c>
       <c r="M408" t="inlineStr">
         <is>
-          <t>Nâng Cấp Độ Vinh Quang</t>
+          <t>Đang tăng Cấp Vinh Quang</t>
         </is>
       </c>
       <c r="N408" t="inlineStr">
@@ -29064,7 +29064,7 @@
       </c>
       <c r="M409" t="inlineStr">
         <is>
-          <t>Sonance Casket Delivery</t>
+          <t>Giao Hòm Thanh Âm</t>
         </is>
       </c>
       <c r="N409" t="inlineStr">
@@ -29134,7 +29134,7 @@
       </c>
       <c r="M410" t="inlineStr">
         <is>
-          <t>Simulation Training Ground</t>
+          <t>Khu Huấn Luyện Mô Phỏng</t>
         </is>
       </c>
       <c r="N410" t="inlineStr">
@@ -29204,7 +29204,7 @@
       </c>
       <c r="M411" t="inlineStr">
         <is>
-          <t>Deck Building</t>
+          <t>Đang xây dựng Bộ bài</t>
         </is>
       </c>
       <c r="N411" t="inlineStr">
@@ -29274,7 +29274,7 @@
       </c>
       <c r="M412" t="inlineStr">
         <is>
-          <t>Deck Composition</t>
+          <t>Thành phần Bộ bài</t>
         </is>
       </c>
       <c r="N412" t="inlineStr">
@@ -29344,7 +29344,7 @@
       </c>
       <c r="M413" t="inlineStr">
         <is>
-          <t>Thử Thách Echo Cruisewing</t>
+          <t>Thử Thách Tiếng Vọng Cruisewing</t>
         </is>
       </c>
       <c r="N413" t="inlineStr">
@@ -29414,7 +29414,7 @@
       </c>
       <c r="M414" t="inlineStr">
         <is>
-          <t>Đang triển khai Echoes</t>
+          <t>Đang triển khai Echo</t>
         </is>
       </c>
       <c r="N414" t="inlineStr">
@@ -29484,7 +29484,7 @@
       </c>
       <c r="M415" t="inlineStr">
         <is>
-          <t>Reconstructing Echoes</t>
+          <t>Đang tái cấu trúc Echo</t>
         </is>
       </c>
       <c r="N415" t="inlineStr">
@@ -29554,7 +29554,7 @@
       </c>
       <c r="M416" t="inlineStr">
         <is>
-          <t>Basic Rules</t>
+          <t>Quy Tắc Cơ Bản</t>
         </is>
       </c>
       <c r="N416" t="inlineStr">
@@ -29694,7 +29694,7 @@
       </c>
       <c r="M418" t="inlineStr">
         <is>
-          <t>Biến Đổi II</t>
+          <t>Biến hình II</t>
         </is>
       </c>
       <c r="N418" t="inlineStr">
@@ -29764,7 +29764,7 @@
       </c>
       <c r="M419" t="inlineStr">
         <is>
-          <t>Biến Đổi III</t>
+          <t>Biến Hình III</t>
         </is>
       </c>
       <c r="N419" t="inlineStr">
@@ -29834,7 +29834,7 @@
       </c>
       <c r="M420" t="inlineStr">
         <is>
-          <t>Biến Đổi I</t>
+          <t>Biến hình I</t>
         </is>
       </c>
       <c r="N420" t="inlineStr">
@@ -29904,7 +29904,7 @@
       </c>
       <c r="M421" t="inlineStr">
         <is>
-          <t>Modulation II</t>
+          <t>Điều Tần II</t>
         </is>
       </c>
       <c r="N421" t="inlineStr">
@@ -29974,7 +29974,7 @@
       </c>
       <c r="M422" t="inlineStr">
         <is>
-          <t>Modulation III</t>
+          <t>Điều Tần III</t>
         </is>
       </c>
       <c r="N422" t="inlineStr">
@@ -30044,7 +30044,7 @@
       </c>
       <c r="M423" t="inlineStr">
         <is>
-          <t>Modulation IV</t>
+          <t>Điều Tần IV</t>
         </is>
       </c>
       <c r="N423" t="inlineStr">
@@ -30114,7 +30114,7 @@
       </c>
       <c r="M424" t="inlineStr">
         <is>
-          <t>Modulation I</t>
+          <t>Điều Tần I</t>
         </is>
       </c>
       <c r="N424" t="inlineStr">
@@ -30184,7 +30184,7 @@
       </c>
       <c r="M425" t="inlineStr">
         <is>
-          <t>Special Skill II</t>
+          <t>Kỹ Năng Đặc Biệt II</t>
         </is>
       </c>
       <c r="N425" t="inlineStr">
@@ -30254,7 +30254,7 @@
       </c>
       <c r="M426" t="inlineStr">
         <is>
-          <t>Special Skill III</t>
+          <t>Kỹ Năng Đặc Biệt III</t>
         </is>
       </c>
       <c r="N426" t="inlineStr">
@@ -30324,7 +30324,7 @@
       </c>
       <c r="M427" t="inlineStr">
         <is>
-          <t>Special Skill I</t>
+          <t>Kỹ Năng Đặc Biệt I</t>
         </is>
       </c>
       <c r="N427" t="inlineStr">
@@ -30394,7 +30394,7 @@
       </c>
       <c r="M428" t="inlineStr">
         <is>
-          <t>Core Echo II</t>
+          <t>Tiếng Vọng Cốt Lõi II</t>
         </is>
       </c>
       <c r="N428" t="inlineStr">
@@ -30464,7 +30464,7 @@
       </c>
       <c r="M429" t="inlineStr">
         <is>
-          <t>Sonance Casket</t>
+          <t>Hòm Thanh Âm</t>
         </is>
       </c>
       <c r="N429" t="inlineStr">
@@ -30604,7 +30604,7 @@
       </c>
       <c r="M431" t="inlineStr">
         <is>
-          <t>Training Dummy</t>
+          <t>Bù Nhìn Huấn Luyện</t>
         </is>
       </c>
       <c r="N431" t="inlineStr">
@@ -30674,7 +30674,7 @@
       </c>
       <c r="M432" t="inlineStr">
         <is>
-          <t>Mục Tiêu Bay Lượn</t>
+          <t>Mục Tiêu Bay Lơ Lửng</t>
         </is>
       </c>
       <c r="N432" t="inlineStr">
@@ -30744,7 +30744,7 @@
       </c>
       <c r="M433" t="inlineStr">
         <is>
-          <t>Propulsion Flux</t>
+          <t>Dòng Đẩy Xung Lực</t>
         </is>
       </c>
       <c r="N433" t="inlineStr">
@@ -30814,7 +30814,7 @@
       </c>
       <c r="M434" t="inlineStr">
         <is>
-          <t>Cấp Độ Liên Minh &amp; Kinh Nghiệm Liên Minh</t>
+          <t>Cấp Liên Minh &amp; Kinh nghiệm</t>
         </is>
       </c>
       <c r="N434" t="inlineStr">
@@ -30884,7 +30884,7 @@
       </c>
       <c r="M435" t="inlineStr">
         <is>
-          <t>Cấp Độ Kho Dữ Liệu</t>
+          <t>Cấp Độ Ngân Hàng Dữ Liệu</t>
         </is>
       </c>
       <c r="N435" t="inlineStr">
@@ -30954,7 +30954,7 @@
       </c>
       <c r="M436" t="inlineStr">
         <is>
-          <t>Thử Thách Echo: Gulpuff</t>
+          <t>Thử Thách Tiếng Vọng: Gulpuff</t>
         </is>
       </c>
       <c r="N436" t="inlineStr">
@@ -31094,7 +31094,7 @@
       </c>
       <c r="M438" t="inlineStr">
         <is>
-          <t>Capture Frequency Signal: I</t>
+          <t>Thu Tần Số: I</t>
         </is>
       </c>
       <c r="N438" t="inlineStr">
@@ -31164,7 +31164,7 @@
       </c>
       <c r="M439" t="inlineStr">
         <is>
-          <t>Capture Frequency Signal: II</t>
+          <t>Thu Tần Số: II</t>
         </is>
       </c>
       <c r="N439" t="inlineStr">
@@ -31234,7 +31234,7 @@
       </c>
       <c r="M440" t="inlineStr">
         <is>
-          <t>Acoustic Print</t>
+          <t>Dấu Âm Thanh</t>
         </is>
       </c>
       <c r="N440" t="inlineStr">
@@ -31304,7 +31304,7 @@
       </c>
       <c r="M441" t="inlineStr">
         <is>
-          <t>Zoom Camera: I</t>
+          <t>Thu nhỏ/Góc rộng: I</t>
         </is>
       </c>
       <c r="N441" t="inlineStr">
@@ -31374,7 +31374,7 @@
       </c>
       <c r="M442" t="inlineStr">
         <is>
-          <t>Incinero Petal</t>
+          <t>Cánh Hoa Incinero</t>
         </is>
       </c>
       <c r="N442" t="inlineStr">
@@ -31444,7 +31444,7 @@
       </c>
       <c r="M443" t="inlineStr">
         <is>
-          <t>Spear Tip: Penetration Test</t>
+          <t>Thử Nghiệm Khả Năng Xuyên Thấu Đầu Lao</t>
         </is>
       </c>
       <c r="N443" t="inlineStr">
@@ -31514,7 +31514,7 @@
       </c>
       <c r="M444" t="inlineStr">
         <is>
-          <t>Spear Breech: Propeller Test</t>
+          <t>Thử Nghiệm Cánh Quạt Đuôi Lao</t>
         </is>
       </c>
       <c r="N444" t="inlineStr">
@@ -31584,7 +31584,7 @@
       </c>
       <c r="M445" t="inlineStr">
         <is>
-          <t>Spear Breech: Propeller Test</t>
+          <t>Thử Nghiệm Cánh Quạt Đuôi Lao</t>
         </is>
       </c>
       <c r="N445" t="inlineStr">
@@ -31654,7 +31654,7 @@
       </c>
       <c r="M446" t="inlineStr">
         <is>
-          <t>Spear Barrel: Durability Test</t>
+          <t>Thử Nghiệm Độ Bền Thân Lao</t>
         </is>
       </c>
       <c r="N446" t="inlineStr">
@@ -31724,7 +31724,7 @@
       </c>
       <c r="M447" t="inlineStr">
         <is>
-          <t>Spear Barrel: Durability Test</t>
+          <t>Thử Nghiệm Độ Bền Thân Lao</t>
         </is>
       </c>
       <c r="N447" t="inlineStr">
@@ -31794,7 +31794,7 @@
       </c>
       <c r="M448" t="inlineStr">
         <is>
-          <t>Explosive Spear</t>
+          <t>Thương Nổ</t>
         </is>
       </c>
       <c r="N448" t="inlineStr">
@@ -31864,7 +31864,7 @@
       </c>
       <c r="M449" t="inlineStr">
         <is>
-          <t>Biến Hình thành Inferno Rider: II</t>
+          <t>Biến hình thành Kỵ Sĩ Hỏa Ngục: II</t>
         </is>
       </c>
       <c r="N449" t="inlineStr">
@@ -31934,7 +31934,7 @@
       </c>
       <c r="M450" t="inlineStr">
         <is>
-          <t>Biến Hình thành Inferno Rider: I</t>
+          <t>Biến hình thành Kỵ Sĩ Hỏa Ngục: I</t>
         </is>
       </c>
       <c r="N450" t="inlineStr">
@@ -32004,7 +32004,7 @@
       </c>
       <c r="M451" t="inlineStr">
         <is>
-          <t>Ultrasonic Pulse Chip</t>
+          <t>Chip Xung Siêu Âm</t>
         </is>
       </c>
       <c r="N451" t="inlineStr">
@@ -32074,7 +32074,7 @@
       </c>
       <c r="M452" t="inlineStr">
         <is>
-          <t>Swamp Vortex</t>
+          <t>Xoáy Lầy Tử Thần</t>
         </is>
       </c>
       <c r="N452" t="inlineStr">
@@ -32144,7 +32144,7 @@
       </c>
       <c r="M453" t="inlineStr">
         <is>
-          <t>Suppressor</t>
+          <t>Bộ Áp Chế</t>
         </is>
       </c>
       <c r="N453" t="inlineStr">
@@ -32214,7 +32214,7 @@
       </c>
       <c r="M454" t="inlineStr">
         <is>
-          <t>Mud</t>
+          <t>Bùn đất</t>
         </is>
       </c>
       <c r="N454" t="inlineStr">
@@ -32284,7 +32284,7 @@
       </c>
       <c r="M455" t="inlineStr">
         <is>
-          <t>Clear Toxic Spores: Offshoot Core</t>
+          <t>Diệt trừ Bào Tử Độc: Nhân Tâm Nhánh</t>
         </is>
       </c>
       <c r="N455" t="inlineStr">
@@ -32354,7 +32354,7 @@
       </c>
       <c r="M456" t="inlineStr">
         <is>
-          <t>Zoom Camera: II</t>
+          <t>Thu nhỏ/Góc rộng: II</t>
         </is>
       </c>
       <c r="N456" t="inlineStr">
@@ -32424,7 +32424,7 @@
       </c>
       <c r="M457" t="inlineStr">
         <is>
-          <t>Zoom Camera: III</t>
+          <t>Thu nhỏ/Góc rộng: III</t>
         </is>
       </c>
       <c r="N457" t="inlineStr">
@@ -32494,7 +32494,7 @@
       </c>
       <c r="M458" t="inlineStr">
         <is>
-          <t>Intensive Training</t>
+          <t>Huấn Luyện Cường Độ Cao</t>
         </is>
       </c>
       <c r="N458" t="inlineStr">
@@ -32564,7 +32564,7 @@
       </c>
       <c r="M459" t="inlineStr">
         <is>
-          <t>About Bountiful Crescendo</t>
+          <t>Về Bản Giao Hưởng Sung Túc</t>
         </is>
       </c>
       <c r="N459" t="inlineStr">
@@ -32634,7 +32634,7 @@
       </c>
       <c r="M460" t="inlineStr">
         <is>
-          <t>Chord Cleansing</t>
+          <t>Thanh Tẩy Giai Điệu</t>
         </is>
       </c>
       <c r="N460" t="inlineStr">
@@ -32704,7 +32704,7 @@
       </c>
       <c r="M461" t="inlineStr">
         <is>
-          <t>Companion Stories</t>
+          <t>Câu Chuyện Đồng Hành</t>
         </is>
       </c>
       <c r="N461" t="inlineStr">
@@ -32844,7 +32844,7 @@
       </c>
       <c r="M463" t="inlineStr">
         <is>
-          <t>[Wuthering Exploration] Mô Tả Sự Kiện</t>
+          <t>["Khám Phá Hư Vô" Mô Tả Sự Kiện</t>
         </is>
       </c>
       <c r="N463" t="inlineStr">
@@ -32914,7 +32914,7 @@
       </c>
       <c r="M464" t="inlineStr">
         <is>
-          <t>Về "Dấu Vết Núi Firmament"</t>
+          <t>Về "Dấu vết của Mt. Firmament"</t>
         </is>
       </c>
       <c r="N464" t="inlineStr">
@@ -32984,7 +32984,7 @@
       </c>
       <c r="M465" t="inlineStr">
         <is>
-          <t>Về Thang Đo Quá Khứ</t>
+          <t>Về *Scale of Past*</t>
         </is>
       </c>
       <c r="N465" t="inlineStr">
@@ -33054,7 +33054,7 @@
       </c>
       <c r="M466" t="inlineStr">
         <is>
-          <t>Solaris Trở Lại Lần Hai</t>
+          <t>Sự Trở Lại Của Solaris</t>
         </is>
       </c>
       <c r="N466" t="inlineStr">
@@ -33124,7 +33124,7 @@
       </c>
       <c r="M467" t="inlineStr">
         <is>
-          <t>Ascendant Aces</t>
+          <t>Thăng Hoa Tinh Anh</t>
         </is>
       </c>
       <c r="N467" t="inlineStr">
@@ -33264,7 +33264,7 @@
       </c>
       <c r="M469" t="inlineStr">
         <is>
-          <t>Max STA Increase</t>
+          <t>Giới hạn STA tăng lên</t>
         </is>
       </c>
       <c r="N469" t="inlineStr">
@@ -33334,7 +33334,7 @@
       </c>
       <c r="M470" t="inlineStr">
         <is>
-          <t>Outro Skill &amp; Intro Skill</t>
+          <t>Kỹ Năng Hồi Kết &amp; Kỹ Năng Khai Chiến</t>
         </is>
       </c>
       <c r="N470" t="inlineStr">
@@ -33404,7 +33404,7 @@
       </c>
       <c r="M471" t="inlineStr">
         <is>
-          <t>Fissured Ledge</t>
+          <t>Vách Đá Nứt</t>
         </is>
       </c>
       <c r="N471" t="inlineStr">
@@ -33474,7 +33474,7 @@
       </c>
       <c r="M472" t="inlineStr">
         <is>
-          <t>Throw Tacetite Fulminate</t>
+          <t>Ném Tacetite Fulminate</t>
         </is>
       </c>
       <c r="N472" t="inlineStr">
@@ -33544,7 +33544,7 @@
       </c>
       <c r="M473" t="inlineStr">
         <is>
-          <t>Electro Flare Effect</t>
+          <t>Hiệu Ứng Điện Quang</t>
         </is>
       </c>
       <c r="N473" t="inlineStr">
@@ -33614,7 +33614,7 @@
       </c>
       <c r="M474" t="inlineStr">
         <is>
-          <t>Aero Erosion Effect: I</t>
+          <t>Hiệu Ứng Aero Erosion: Cấp I</t>
         </is>
       </c>
       <c r="N474" t="inlineStr">
@@ -33684,7 +33684,7 @@
       </c>
       <c r="M475" t="inlineStr">
         <is>
-          <t>Aero Erosion Effect: II</t>
+          <t>Hiệu Ứng Aero Erosion: Cấp II</t>
         </is>
       </c>
       <c r="N475" t="inlineStr">
@@ -33754,7 +33754,7 @@
       </c>
       <c r="M476" t="inlineStr">
         <is>
-          <t>Electro Flare Effect: I</t>
+          <t>Hiệu Ứng Điện Quang: I</t>
         </is>
       </c>
       <c r="N476" t="inlineStr">
@@ -33824,7 +33824,7 @@
       </c>
       <c r="M477" t="inlineStr">
         <is>
-          <t>Electro Flare: II</t>
+          <t>Điện Quang: II</t>
         </is>
       </c>
       <c r="N477" t="inlineStr">
@@ -33894,7 +33894,7 @@
       </c>
       <c r="M478" t="inlineStr">
         <is>
-          <t>Glacio Chafe Effect: I</t>
+          <t>Hiệu Ứng Xước Băng Giá: I</t>
         </is>
       </c>
       <c r="N478" t="inlineStr">
@@ -33964,7 +33964,7 @@
       </c>
       <c r="M479" t="inlineStr">
         <is>
-          <t>Glacio Chafe Effect: II</t>
+          <t>Hiệu ứng Chafe băng giá: II</t>
         </is>
       </c>
       <c r="N479" t="inlineStr">
@@ -34034,7 +34034,7 @@
       </c>
       <c r="M480" t="inlineStr">
         <is>
-          <t>Fusion Burst Effect: I</t>
+          <t>Hiệu ứng Bùng Nổ Hợp Thể: I</t>
         </is>
       </c>
       <c r="N480" t="inlineStr">
@@ -34104,7 +34104,7 @@
       </c>
       <c r="M481" t="inlineStr">
         <is>
-          <t>Fusion Burst Effect: II</t>
+          <t>Hiệu ứng Bùng Nổ Hợp Thể: II</t>
         </is>
       </c>
       <c r="N481" t="inlineStr">
@@ -34174,7 +34174,7 @@
       </c>
       <c r="M482" t="inlineStr">
         <is>
-          <t>Spectro Frazzle Effect: I</t>
+          <t>Hiệu Ứng Rối Loạn Spectro: I</t>
         </is>
       </c>
       <c r="N482" t="inlineStr">
@@ -34244,7 +34244,7 @@
       </c>
       <c r="M483" t="inlineStr">
         <is>
-          <t>Spectro Frazzle Effect: II</t>
+          <t>Hiệu Ứng Rối Loạn Spectro: II</t>
         </is>
       </c>
       <c r="N483" t="inlineStr">
@@ -34314,7 +34314,7 @@
       </c>
       <c r="M484" t="inlineStr">
         <is>
-          <t>Havoc Bane Effect: I</t>
+          <t>Hiệu Ứng Hiểm Họa Havoc: I</t>
         </is>
       </c>
       <c r="N484" t="inlineStr">
@@ -34384,7 +34384,7 @@
       </c>
       <c r="M485" t="inlineStr">
         <is>
-          <t>Havoc Bane Effect: II</t>
+          <t>Hiệu Ứng Hiểm Họa Havoc: II</t>
         </is>
       </c>
       <c r="N485" t="inlineStr">
@@ -34454,7 +34454,7 @@
       </c>
       <c r="M486" t="inlineStr">
         <is>
-          <t>Kích Hoạt Mạch Circuit</t>
+          <t>Kích hoạt Mạch Điện</t>
         </is>
       </c>
       <c r="N486" t="inlineStr">
@@ -34524,7 +34524,7 @@
       </c>
       <c r="M487" t="inlineStr">
         <is>
-          <t>Energy Matrix: II</t>
+          <t>Ma Trận Năng Lượng: Cấp II</t>
         </is>
       </c>
       <c r="N487" t="inlineStr">
@@ -34594,7 +34594,7 @@
       </c>
       <c r="M488" t="inlineStr">
         <is>
-          <t>Encryption Block: II</t>
+          <t>Khối Mã Hóa: II</t>
         </is>
       </c>
       <c r="N488" t="inlineStr">
@@ -34664,7 +34664,7 @@
       </c>
       <c r="M489" t="inlineStr">
         <is>
-          <t>Vine Trap: I</t>
+          <t>Bẫy Dây Leo: Cấp I</t>
         </is>
       </c>
       <c r="N489" t="inlineStr">
@@ -34734,7 +34734,7 @@
       </c>
       <c r="M490" t="inlineStr">
         <is>
-          <t>Vine Trap: II</t>
+          <t>Bẫy Dây Leo: Cấp II</t>
         </is>
       </c>
       <c r="N490" t="inlineStr">
@@ -34804,7 +34804,7 @@
       </c>
       <c r="M491" t="inlineStr">
         <is>
-          <t>Biến Hình Thành Mourning Aix</t>
+          <t>Biến hình thành Mourning Aix</t>
         </is>
       </c>
       <c r="N491" t="inlineStr">
@@ -34874,7 +34874,7 @@
       </c>
       <c r="M492" t="inlineStr">
         <is>
-          <t>Khôi Phục Bích Họa</t>
+          <t>Khôi phục Bích Họa</t>
         </is>
       </c>
       <c r="N492" t="inlineStr">
@@ -34944,7 +34944,7 @@
       </c>
       <c r="M493" t="inlineStr">
         <is>
-          <t>Biến Hình Thành Mourning Aix: I</t>
+          <t>Biến hình Mourning Aix: I</t>
         </is>
       </c>
       <c r="N493" t="inlineStr">
@@ -35014,7 +35014,7 @@
       </c>
       <c r="M494" t="inlineStr">
         <is>
-          <t>Biến Hình Thành Mourning Aix: II</t>
+          <t>Biến hình Mourning Aix: II</t>
         </is>
       </c>
       <c r="N494" t="inlineStr">
@@ -35084,7 +35084,7 @@
       </c>
       <c r="M495" t="inlineStr">
         <is>
-          <t>Biến Hình Thành Mourning Aix: III</t>
+          <t>Biến hình Mourning Aix: III</t>
         </is>
       </c>
       <c r="N495" t="inlineStr">
@@ -35154,7 +35154,7 @@
       </c>
       <c r="M496" t="inlineStr">
         <is>
-          <t>Echo Counter Skill</t>
+          <t>Kỹ Năng Phản Đòn Tiếng Vọng</t>
         </is>
       </c>
       <c r="N496" t="inlineStr">
@@ -35224,7 +35224,7 @@
       </c>
       <c r="M497" t="inlineStr">
         <is>
-          <t>[Alloy Smelt] Event Rules</t>
+          <t>Thể lệ sự kiện [Nấu luyện Hợp Kim]</t>
         </is>
       </c>
       <c r="N497" t="inlineStr">
@@ -35294,7 +35294,7 @@
       </c>
       <c r="M498" t="inlineStr">
         <is>
-          <t>Alloy Smelt II</t>
+          <t>Nấu Luyện Hợp Kim II</t>
         </is>
       </c>
       <c r="N498" t="inlineStr">
@@ -35364,7 +35364,7 @@
       </c>
       <c r="M499" t="inlineStr">
         <is>
-          <t>Chi Tiết Giai Đoạn Luyện Hợp Kim II</t>
+          <t>Chi Tiết Giai Đoạn Nấu Luyện Hợp Kim II</t>
         </is>
       </c>
       <c r="N499" t="inlineStr">
@@ -35434,7 +35434,7 @@
       </c>
       <c r="M500" t="inlineStr">
         <is>
-          <t>Chi Tiết Giai Đoạn Luyện Hợp Kim II</t>
+          <t>Chi Tiết Giai Đoạn Nấu Luyện Hợp Kim II</t>
         </is>
       </c>
       <c r="N500" t="inlineStr">
@@ -35504,7 +35504,7 @@
       </c>
       <c r="M501" t="inlineStr">
         <is>
-          <t>Chi Tiết Giai Đoạn Luyện Hợp Kim II</t>
+          <t>Chi Tiết Giai Đoạn Nấu Luyện Hợp Kim II</t>
         </is>
       </c>
       <c r="N501" t="inlineStr">
